--- a/data/raw/비정형 분석용_핵심 용어 사전집_v1.0.xlsx
+++ b/data/raw/비정형 분석용_핵심 용어 사전집_v1.0.xlsx
@@ -875,7 +875,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V192"/>
+  <dimension ref="A1:V215"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -21978,6 +21978,2582 @@
       <c r="V192" s="16" t="inlineStr">
         <is>
           <t>GH-DIGEST,media_source_fallback_design_2026_09_13.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="193" ht="42" customHeight="1">
+      <c r="A193" s="16" t="inlineStr">
+        <is>
+          <t>TERM-192</t>
+        </is>
+      </c>
+      <c r="B193" s="16" t="inlineStr">
+        <is>
+          <t>농업·농기상</t>
+        </is>
+      </c>
+      <c r="C193" s="16" t="inlineStr">
+        <is>
+          <t>Agriculture &amp; Agrometeorology</t>
+        </is>
+      </c>
+      <c r="D193" s="16" t="inlineStr">
+        <is>
+          <t>생산지역</t>
+        </is>
+      </c>
+      <c r="E193" s="16" t="inlineStr">
+        <is>
+          <t>Production Regions</t>
+        </is>
+      </c>
+      <c r="F193" s="16" t="inlineStr">
+        <is>
+          <t>생산지역</t>
+        </is>
+      </c>
+      <c r="G193" s="16" t="inlineStr">
+        <is>
+          <t>Heilongjiang (China)</t>
+        </is>
+      </c>
+      <c r="H193" s="16" t="inlineStr">
+        <is>
+          <t>헤이룽장</t>
+        </is>
+      </c>
+      <c r="I193" s="16" t="inlineStr">
+        <is>
+          <t>CN_Heilongjiang</t>
+        </is>
+      </c>
+      <c r="J193" s="16" t="inlineStr">
+        <is>
+          <t>Heilongjiang Province; 黑龙江省; 헤이룽장성</t>
+        </is>
+      </c>
+      <c r="K193" s="16" t="inlineStr">
+        <is>
+          <t>Region</t>
+        </is>
+      </c>
+      <c r="L193" s="16" t="inlineStr">
+        <is>
+          <t>중국 대두 재배 지역(tier 1) — 중국 최대 국내 대두 재배 지역</t>
+        </is>
+      </c>
+      <c r="M193" s="16" t="inlineStr">
+        <is>
+          <t>지역별 기후 신호는 일반화하지 않는다(지역 간 단순 평균 금지 — 재배면적 가중 없이는 합산 불가) · 좌표는 행정 중심이 아닌 주산 벨트 중심(NASA POWER 0.5° 격자 감도) · 라벨 CONFIRMED/INFERENCE는 config coord_status와 동기 · 좌표 이동 시 구좌표 수집분과 시계열을 잇지 않는다(vintage 분리)</t>
+        </is>
+      </c>
+      <c r="N193" s="16" t="inlineStr">
+        <is>
+          <t>Supply</t>
+        </is>
+      </c>
+      <c r="O193" s="16" t="inlineStr">
+        <is>
+          <t>CONTEXT</t>
+        </is>
+      </c>
+      <c r="P193" s="16" t="inlineStr">
+        <is>
+          <t>lat/lon(deg)</t>
+        </is>
+      </c>
+      <c r="Q193" s="16" t="inlineStr">
+        <is>
+          <t>정본 좌표 표 §3.2 기준 — 아카이브 daily 8변수(토양 hourly 포함)+예보 FCST_</t>
+        </is>
+      </c>
+      <c r="R193" s="16" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="S193" s="16" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="T193" s="16" t="inlineStr">
+        <is>
+          <t>ProductionRegion</t>
+        </is>
+      </c>
+      <c r="U193" s="16" t="inlineStr">
+        <is>
+          <t>LOCATED_AT</t>
+        </is>
+      </c>
+      <c r="V193" s="16" t="inlineStr">
+        <is>
+          <t>config/production_regions.yaml,climate_regions_forecast_weathernext_2026_09_13.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="194" ht="42" customHeight="1">
+      <c r="A194" s="16" t="inlineStr">
+        <is>
+          <t>TERM-193</t>
+        </is>
+      </c>
+      <c r="B194" s="16" t="inlineStr">
+        <is>
+          <t>농업·농기상</t>
+        </is>
+      </c>
+      <c r="C194" s="16" t="inlineStr">
+        <is>
+          <t>Agriculture &amp; Agrometeorology</t>
+        </is>
+      </c>
+      <c r="D194" s="16" t="inlineStr">
+        <is>
+          <t>생산지역</t>
+        </is>
+      </c>
+      <c r="E194" s="16" t="inlineStr">
+        <is>
+          <t>Production Regions</t>
+        </is>
+      </c>
+      <c r="F194" s="16" t="inlineStr">
+        <is>
+          <t>생산지역</t>
+        </is>
+      </c>
+      <c r="G194" s="16" t="inlineStr">
+        <is>
+          <t>Shandong (China)</t>
+        </is>
+      </c>
+      <c r="H194" s="16" t="inlineStr">
+        <is>
+          <t>산둥</t>
+        </is>
+      </c>
+      <c r="I194" s="16" t="inlineStr">
+        <is>
+          <t>CN_Shandong</t>
+        </is>
+      </c>
+      <c r="J194" s="16" t="inlineStr">
+        <is>
+          <t>Shandong Province; 山东省; 산둥성</t>
+        </is>
+      </c>
+      <c r="K194" s="16" t="inlineStr">
+        <is>
+          <t>Region</t>
+        </is>
+      </c>
+      <c r="L194" s="16" t="inlineStr">
+        <is>
+          <t>중국 대두 압착 지역(tier 1) — 연안 최대 압착 클러스터</t>
+        </is>
+      </c>
+      <c r="M194" s="16" t="inlineStr">
+        <is>
+          <t>지역별 기후 신호는 일반화하지 않는다(지역 간 단순 평균 금지 — 재배면적 가중 없이는 합산 불가) · 좌표는 행정 중심이 아닌 주산 벨트 중심(NASA POWER 0.5° 격자 감도) · 라벨 CONFIRMED/INFERENCE는 config coord_status와 동기 · 좌표 이동 시 구좌표 수집분과 시계열을 잇지 않는다(vintage 분리)</t>
+        </is>
+      </c>
+      <c r="N194" s="16" t="inlineStr">
+        <is>
+          <t>Supply</t>
+        </is>
+      </c>
+      <c r="O194" s="16" t="inlineStr">
+        <is>
+          <t>CONTEXT</t>
+        </is>
+      </c>
+      <c r="P194" s="16" t="inlineStr">
+        <is>
+          <t>lat/lon(deg)</t>
+        </is>
+      </c>
+      <c r="Q194" s="16" t="inlineStr">
+        <is>
+          <t>정본 좌표 표 §3.2 기준 — 아카이브 daily 8변수(토양 hourly 포함)+예보 FCST_</t>
+        </is>
+      </c>
+      <c r="R194" s="16" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="S194" s="16" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="T194" s="16" t="inlineStr">
+        <is>
+          <t>ProductionRegion</t>
+        </is>
+      </c>
+      <c r="U194" s="16" t="inlineStr">
+        <is>
+          <t>LOCATED_AT</t>
+        </is>
+      </c>
+      <c r="V194" s="16" t="inlineStr">
+        <is>
+          <t>config/production_regions.yaml,climate_regions_forecast_weathernext_2026_09_13.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="195" ht="42" customHeight="1">
+      <c r="A195" s="16" t="inlineStr">
+        <is>
+          <t>TERM-194</t>
+        </is>
+      </c>
+      <c r="B195" s="16" t="inlineStr">
+        <is>
+          <t>농업·농기상</t>
+        </is>
+      </c>
+      <c r="C195" s="16" t="inlineStr">
+        <is>
+          <t>Agriculture &amp; Agrometeorology</t>
+        </is>
+      </c>
+      <c r="D195" s="16" t="inlineStr">
+        <is>
+          <t>생산지역</t>
+        </is>
+      </c>
+      <c r="E195" s="16" t="inlineStr">
+        <is>
+          <t>Production Regions</t>
+        </is>
+      </c>
+      <c r="F195" s="16" t="inlineStr">
+        <is>
+          <t>생산지역</t>
+        </is>
+      </c>
+      <c r="G195" s="16" t="inlineStr">
+        <is>
+          <t>Jiangsu (China)</t>
+        </is>
+      </c>
+      <c r="H195" s="16" t="inlineStr">
+        <is>
+          <t>장쑤</t>
+        </is>
+      </c>
+      <c r="I195" s="16" t="inlineStr">
+        <is>
+          <t>CN_Jiangsu</t>
+        </is>
+      </c>
+      <c r="J195" s="16" t="inlineStr">
+        <is>
+          <t>Jiangsu Province; 江苏省; 장쑤성</t>
+        </is>
+      </c>
+      <c r="K195" s="16" t="inlineStr">
+        <is>
+          <t>Region</t>
+        </is>
+      </c>
+      <c r="L195" s="16" t="inlineStr">
+        <is>
+          <t>중국 대두 압착 지역(tier 1) — 양쯔강 압착 허브</t>
+        </is>
+      </c>
+      <c r="M195" s="16" t="inlineStr">
+        <is>
+          <t>지역별 기후 신호는 일반화하지 않는다(지역 간 단순 평균 금지 — 재배면적 가중 없이는 합산 불가) · 좌표는 행정 중심이 아닌 주산 벨트 중심(NASA POWER 0.5° 격자 감도) · 라벨 CONFIRMED/INFERENCE는 config coord_status와 동기 · 좌표 이동 시 구좌표 수집분과 시계열을 잇지 않는다(vintage 분리)</t>
+        </is>
+      </c>
+      <c r="N195" s="16" t="inlineStr">
+        <is>
+          <t>Supply</t>
+        </is>
+      </c>
+      <c r="O195" s="16" t="inlineStr">
+        <is>
+          <t>CONTEXT</t>
+        </is>
+      </c>
+      <c r="P195" s="16" t="inlineStr">
+        <is>
+          <t>lat/lon(deg)</t>
+        </is>
+      </c>
+      <c r="Q195" s="16" t="inlineStr">
+        <is>
+          <t>정본 좌표 표 §3.2 기준 — 아카이브 daily 8변수(토양 hourly 포함)+예보 FCST_</t>
+        </is>
+      </c>
+      <c r="R195" s="16" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="S195" s="16" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="T195" s="16" t="inlineStr">
+        <is>
+          <t>ProductionRegion</t>
+        </is>
+      </c>
+      <c r="U195" s="16" t="inlineStr">
+        <is>
+          <t>LOCATED_AT</t>
+        </is>
+      </c>
+      <c r="V195" s="16" t="inlineStr">
+        <is>
+          <t>config/production_regions.yaml,climate_regions_forecast_weathernext_2026_09_13.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="196" ht="42" customHeight="1">
+      <c r="A196" s="16" t="inlineStr">
+        <is>
+          <t>TERM-195</t>
+        </is>
+      </c>
+      <c r="B196" s="16" t="inlineStr">
+        <is>
+          <t>농업·농기상</t>
+        </is>
+      </c>
+      <c r="C196" s="16" t="inlineStr">
+        <is>
+          <t>Agriculture &amp; Agrometeorology</t>
+        </is>
+      </c>
+      <c r="D196" s="16" t="inlineStr">
+        <is>
+          <t>생산지역</t>
+        </is>
+      </c>
+      <c r="E196" s="16" t="inlineStr">
+        <is>
+          <t>Production Regions</t>
+        </is>
+      </c>
+      <c r="F196" s="16" t="inlineStr">
+        <is>
+          <t>생산지역</t>
+        </is>
+      </c>
+      <c r="G196" s="16" t="inlineStr">
+        <is>
+          <t>Illinois (USA)</t>
+        </is>
+      </c>
+      <c r="H196" s="16" t="inlineStr">
+        <is>
+          <t>일리노이</t>
+        </is>
+      </c>
+      <c r="I196" s="16" t="inlineStr">
+        <is>
+          <t>US_Illinois</t>
+        </is>
+      </c>
+      <c r="J196" s="16" t="inlineStr">
+        <is>
+          <t>Illinois; IL; 일리노이주</t>
+        </is>
+      </c>
+      <c r="K196" s="16" t="inlineStr">
+        <is>
+          <t>Region</t>
+        </is>
+      </c>
+      <c r="L196" s="16" t="inlineStr">
+        <is>
+          <t>미국 대두 재배·압착 지역(tier 1) — 미국 생산 1위 주</t>
+        </is>
+      </c>
+      <c r="M196" s="16" t="inlineStr">
+        <is>
+          <t>지역별 기후 신호는 일반화하지 않는다(지역 간 단순 평균 금지 — 재배면적 가중 없이는 합산 불가) · 좌표는 행정 중심이 아닌 주산 벨트 중심(NASA POWER 0.5° 격자 감도) · 라벨 CONFIRMED/INFERENCE는 config coord_status와 동기 · 좌표 이동 시 구좌표 수집분과 시계열을 잇지 않는다(vintage 분리)</t>
+        </is>
+      </c>
+      <c r="N196" s="16" t="inlineStr">
+        <is>
+          <t>Supply</t>
+        </is>
+      </c>
+      <c r="O196" s="16" t="inlineStr">
+        <is>
+          <t>CONTEXT</t>
+        </is>
+      </c>
+      <c r="P196" s="16" t="inlineStr">
+        <is>
+          <t>lat/lon(deg)</t>
+        </is>
+      </c>
+      <c r="Q196" s="16" t="inlineStr">
+        <is>
+          <t>정본 좌표 표 §3.2 기준 — 아카이브 daily 8변수(토양 hourly 포함)+예보 FCST_</t>
+        </is>
+      </c>
+      <c r="R196" s="16" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="S196" s="16" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="T196" s="16" t="inlineStr">
+        <is>
+          <t>ProductionRegion</t>
+        </is>
+      </c>
+      <c r="U196" s="16" t="inlineStr">
+        <is>
+          <t>LOCATED_AT</t>
+        </is>
+      </c>
+      <c r="V196" s="16" t="inlineStr">
+        <is>
+          <t>config/production_regions.yaml,climate_regions_forecast_weathernext_2026_09_13.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="197" ht="42" customHeight="1">
+      <c r="A197" s="16" t="inlineStr">
+        <is>
+          <t>TERM-196</t>
+        </is>
+      </c>
+      <c r="B197" s="16" t="inlineStr">
+        <is>
+          <t>농업·농기상</t>
+        </is>
+      </c>
+      <c r="C197" s="16" t="inlineStr">
+        <is>
+          <t>Agriculture &amp; Agrometeorology</t>
+        </is>
+      </c>
+      <c r="D197" s="16" t="inlineStr">
+        <is>
+          <t>생산지역</t>
+        </is>
+      </c>
+      <c r="E197" s="16" t="inlineStr">
+        <is>
+          <t>Production Regions</t>
+        </is>
+      </c>
+      <c r="F197" s="16" t="inlineStr">
+        <is>
+          <t>생산지역</t>
+        </is>
+      </c>
+      <c r="G197" s="16" t="inlineStr">
+        <is>
+          <t>Iowa (USA)</t>
+        </is>
+      </c>
+      <c r="H197" s="16" t="inlineStr">
+        <is>
+          <t>아이오와</t>
+        </is>
+      </c>
+      <c r="I197" s="16" t="inlineStr">
+        <is>
+          <t>US_Iowa</t>
+        </is>
+      </c>
+      <c r="J197" s="16" t="inlineStr">
+        <is>
+          <t>Iowa; IA; 아이오와주</t>
+        </is>
+      </c>
+      <c r="K197" s="16" t="inlineStr">
+        <is>
+          <t>Region</t>
+        </is>
+      </c>
+      <c r="L197" s="16" t="inlineStr">
+        <is>
+          <t>미국 대두 재배·압착 지역(tier 1) — 미국 압착 설비 1위 주</t>
+        </is>
+      </c>
+      <c r="M197" s="16" t="inlineStr">
+        <is>
+          <t>지역별 기후 신호는 일반화하지 않는다(지역 간 단순 평균 금지 — 재배면적 가중 없이는 합산 불가) · 좌표는 행정 중심이 아닌 주산 벨트 중심(NASA POWER 0.5° 격자 감도) · 라벨 CONFIRMED/INFERENCE는 config coord_status와 동기 · 좌표 이동 시 구좌표 수집분과 시계열을 잇지 않는다(vintage 분리)</t>
+        </is>
+      </c>
+      <c r="N197" s="16" t="inlineStr">
+        <is>
+          <t>Supply</t>
+        </is>
+      </c>
+      <c r="O197" s="16" t="inlineStr">
+        <is>
+          <t>CONTEXT</t>
+        </is>
+      </c>
+      <c r="P197" s="16" t="inlineStr">
+        <is>
+          <t>lat/lon(deg)</t>
+        </is>
+      </c>
+      <c r="Q197" s="16" t="inlineStr">
+        <is>
+          <t>정본 좌표 표 §3.2 기준 — 아카이브 daily 8변수(토양 hourly 포함)+예보 FCST_</t>
+        </is>
+      </c>
+      <c r="R197" s="16" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="S197" s="16" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="T197" s="16" t="inlineStr">
+        <is>
+          <t>ProductionRegion</t>
+        </is>
+      </c>
+      <c r="U197" s="16" t="inlineStr">
+        <is>
+          <t>LOCATED_AT</t>
+        </is>
+      </c>
+      <c r="V197" s="16" t="inlineStr">
+        <is>
+          <t>config/production_regions.yaml,climate_regions_forecast_weathernext_2026_09_13.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="198" ht="42" customHeight="1">
+      <c r="A198" s="16" t="inlineStr">
+        <is>
+          <t>TERM-197</t>
+        </is>
+      </c>
+      <c r="B198" s="16" t="inlineStr">
+        <is>
+          <t>농업·농기상</t>
+        </is>
+      </c>
+      <c r="C198" s="16" t="inlineStr">
+        <is>
+          <t>Agriculture &amp; Agrometeorology</t>
+        </is>
+      </c>
+      <c r="D198" s="16" t="inlineStr">
+        <is>
+          <t>생산지역</t>
+        </is>
+      </c>
+      <c r="E198" s="16" t="inlineStr">
+        <is>
+          <t>Production Regions</t>
+        </is>
+      </c>
+      <c r="F198" s="16" t="inlineStr">
+        <is>
+          <t>생산지역</t>
+        </is>
+      </c>
+      <c r="G198" s="16" t="inlineStr">
+        <is>
+          <t>Indiana (USA)</t>
+        </is>
+      </c>
+      <c r="H198" s="16" t="inlineStr">
+        <is>
+          <t>인디애나</t>
+        </is>
+      </c>
+      <c r="I198" s="16" t="inlineStr">
+        <is>
+          <t>US_Indiana</t>
+        </is>
+      </c>
+      <c r="J198" s="16" t="inlineStr">
+        <is>
+          <t>Indiana; IN; 인디애나주</t>
+        </is>
+      </c>
+      <c r="K198" s="16" t="inlineStr">
+        <is>
+          <t>Region</t>
+        </is>
+      </c>
+      <c r="L198" s="16" t="inlineStr">
+        <is>
+          <t>미국 대두 재배 지역(tier 1) — 미국 생산 3위 주</t>
+        </is>
+      </c>
+      <c r="M198" s="16" t="inlineStr">
+        <is>
+          <t>지역별 기후 신호는 일반화하지 않는다(지역 간 단순 평균 금지 — 재배면적 가중 없이는 합산 불가) · 좌표는 행정 중심이 아닌 주산 벨트 중심(NASA POWER 0.5° 격자 감도) · 라벨 CONFIRMED/INFERENCE는 config coord_status와 동기 · 좌표 이동 시 구좌표 수집분과 시계열을 잇지 않는다(vintage 분리)</t>
+        </is>
+      </c>
+      <c r="N198" s="16" t="inlineStr">
+        <is>
+          <t>Supply</t>
+        </is>
+      </c>
+      <c r="O198" s="16" t="inlineStr">
+        <is>
+          <t>CONTEXT</t>
+        </is>
+      </c>
+      <c r="P198" s="16" t="inlineStr">
+        <is>
+          <t>lat/lon(deg)</t>
+        </is>
+      </c>
+      <c r="Q198" s="16" t="inlineStr">
+        <is>
+          <t>정본 좌표 표 §3.2 기준 — 아카이브 daily 8변수(토양 hourly 포함)+예보 FCST_</t>
+        </is>
+      </c>
+      <c r="R198" s="16" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="S198" s="16" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="T198" s="16" t="inlineStr">
+        <is>
+          <t>ProductionRegion</t>
+        </is>
+      </c>
+      <c r="U198" s="16" t="inlineStr">
+        <is>
+          <t>LOCATED_AT</t>
+        </is>
+      </c>
+      <c r="V198" s="16" t="inlineStr">
+        <is>
+          <t>config/production_regions.yaml,climate_regions_forecast_weathernext_2026_09_13.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="199" ht="42" customHeight="1">
+      <c r="A199" s="16" t="inlineStr">
+        <is>
+          <t>TERM-198</t>
+        </is>
+      </c>
+      <c r="B199" s="16" t="inlineStr">
+        <is>
+          <t>농업·농기상</t>
+        </is>
+      </c>
+      <c r="C199" s="16" t="inlineStr">
+        <is>
+          <t>Agriculture &amp; Agrometeorology</t>
+        </is>
+      </c>
+      <c r="D199" s="16" t="inlineStr">
+        <is>
+          <t>생산지역</t>
+        </is>
+      </c>
+      <c r="E199" s="16" t="inlineStr">
+        <is>
+          <t>Production Regions</t>
+        </is>
+      </c>
+      <c r="F199" s="16" t="inlineStr">
+        <is>
+          <t>생산지역</t>
+        </is>
+      </c>
+      <c r="G199" s="16" t="inlineStr">
+        <is>
+          <t>Mato Grosso (Brazil)</t>
+        </is>
+      </c>
+      <c r="H199" s="16" t="inlineStr">
+        <is>
+          <t>마투그로수</t>
+        </is>
+      </c>
+      <c r="I199" s="16" t="inlineStr">
+        <is>
+          <t>BR_MatoGrosso</t>
+        </is>
+      </c>
+      <c r="J199" s="16" t="inlineStr">
+        <is>
+          <t>Mato Grosso; MT (Brazil); 마투그로수주</t>
+        </is>
+      </c>
+      <c r="K199" s="16" t="inlineStr">
+        <is>
+          <t>Region</t>
+        </is>
+      </c>
+      <c r="L199" s="16" t="inlineStr">
+        <is>
+          <t>브라질 대두 재배·압착 지역(tier 1) — 브라질 생산 1위 주</t>
+        </is>
+      </c>
+      <c r="M199" s="16" t="inlineStr">
+        <is>
+          <t>지역별 기후 신호는 일반화하지 않는다(지역 간 단순 평균 금지 — 재배면적 가중 없이는 합산 불가) · 좌표는 행정 중심이 아닌 주산 벨트 중심(NASA POWER 0.5° 격자 감도) · 라벨 CONFIRMED/INFERENCE는 config coord_status와 동기 · 좌표 이동 시 구좌표 수집분과 시계열을 잇지 않는다(vintage 분리)</t>
+        </is>
+      </c>
+      <c r="N199" s="16" t="inlineStr">
+        <is>
+          <t>Supply</t>
+        </is>
+      </c>
+      <c r="O199" s="16" t="inlineStr">
+        <is>
+          <t>CONTEXT</t>
+        </is>
+      </c>
+      <c r="P199" s="16" t="inlineStr">
+        <is>
+          <t>lat/lon(deg)</t>
+        </is>
+      </c>
+      <c r="Q199" s="16" t="inlineStr">
+        <is>
+          <t>정본 좌표 표 §3.2 기준 — 아카이브 daily 8변수(토양 hourly 포함)+예보 FCST_</t>
+        </is>
+      </c>
+      <c r="R199" s="16" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="S199" s="16" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="T199" s="16" t="inlineStr">
+        <is>
+          <t>ProductionRegion</t>
+        </is>
+      </c>
+      <c r="U199" s="16" t="inlineStr">
+        <is>
+          <t>LOCATED_AT</t>
+        </is>
+      </c>
+      <c r="V199" s="16" t="inlineStr">
+        <is>
+          <t>config/production_regions.yaml,climate_regions_forecast_weathernext_2026_09_13.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="200" ht="42" customHeight="1">
+      <c r="A200" s="16" t="inlineStr">
+        <is>
+          <t>TERM-199</t>
+        </is>
+      </c>
+      <c r="B200" s="16" t="inlineStr">
+        <is>
+          <t>농업·농기상</t>
+        </is>
+      </c>
+      <c r="C200" s="16" t="inlineStr">
+        <is>
+          <t>Agriculture &amp; Agrometeorology</t>
+        </is>
+      </c>
+      <c r="D200" s="16" t="inlineStr">
+        <is>
+          <t>생산지역</t>
+        </is>
+      </c>
+      <c r="E200" s="16" t="inlineStr">
+        <is>
+          <t>Production Regions</t>
+        </is>
+      </c>
+      <c r="F200" s="16" t="inlineStr">
+        <is>
+          <t>생산지역</t>
+        </is>
+      </c>
+      <c r="G200" s="16" t="inlineStr">
+        <is>
+          <t>Paraná (Brazil)</t>
+        </is>
+      </c>
+      <c r="H200" s="16" t="inlineStr">
+        <is>
+          <t>파라나</t>
+        </is>
+      </c>
+      <c r="I200" s="16" t="inlineStr">
+        <is>
+          <t>BR_Parana</t>
+        </is>
+      </c>
+      <c r="J200" s="16" t="inlineStr">
+        <is>
+          <t>Parana; PR (Brazil); 파라나주</t>
+        </is>
+      </c>
+      <c r="K200" s="16" t="inlineStr">
+        <is>
+          <t>Region</t>
+        </is>
+      </c>
+      <c r="L200" s="16" t="inlineStr">
+        <is>
+          <t>브라질 대두 재배·압착 지역(tier 1) — 브라질 주요 유지 가공 주</t>
+        </is>
+      </c>
+      <c r="M200" s="16" t="inlineStr">
+        <is>
+          <t>지역별 기후 신호는 일반화하지 않는다(지역 간 단순 평균 금지 — 재배면적 가중 없이는 합산 불가) · 좌표는 행정 중심이 아닌 주산 벨트 중심(NASA POWER 0.5° 격자 감도) · 라벨 CONFIRMED/INFERENCE는 config coord_status와 동기 · 좌표 이동 시 구좌표 수집분과 시계열을 잇지 않는다(vintage 분리)</t>
+        </is>
+      </c>
+      <c r="N200" s="16" t="inlineStr">
+        <is>
+          <t>Supply</t>
+        </is>
+      </c>
+      <c r="O200" s="16" t="inlineStr">
+        <is>
+          <t>CONTEXT</t>
+        </is>
+      </c>
+      <c r="P200" s="16" t="inlineStr">
+        <is>
+          <t>lat/lon(deg)</t>
+        </is>
+      </c>
+      <c r="Q200" s="16" t="inlineStr">
+        <is>
+          <t>정본 좌표 표 §3.2 기준 — 아카이브 daily 8변수(토양 hourly 포함)+예보 FCST_</t>
+        </is>
+      </c>
+      <c r="R200" s="16" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="S200" s="16" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="T200" s="16" t="inlineStr">
+        <is>
+          <t>ProductionRegion</t>
+        </is>
+      </c>
+      <c r="U200" s="16" t="inlineStr">
+        <is>
+          <t>LOCATED_AT</t>
+        </is>
+      </c>
+      <c r="V200" s="16" t="inlineStr">
+        <is>
+          <t>config/production_regions.yaml,climate_regions_forecast_weathernext_2026_09_13.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="201" ht="42" customHeight="1">
+      <c r="A201" s="16" t="inlineStr">
+        <is>
+          <t>TERM-200</t>
+        </is>
+      </c>
+      <c r="B201" s="16" t="inlineStr">
+        <is>
+          <t>농업·농기상</t>
+        </is>
+      </c>
+      <c r="C201" s="16" t="inlineStr">
+        <is>
+          <t>Agriculture &amp; Agrometeorology</t>
+        </is>
+      </c>
+      <c r="D201" s="16" t="inlineStr">
+        <is>
+          <t>생산지역</t>
+        </is>
+      </c>
+      <c r="E201" s="16" t="inlineStr">
+        <is>
+          <t>Production Regions</t>
+        </is>
+      </c>
+      <c r="F201" s="16" t="inlineStr">
+        <is>
+          <t>생산지역</t>
+        </is>
+      </c>
+      <c r="G201" s="16" t="inlineStr">
+        <is>
+          <t>Mato Grosso do Sul (Brazil)</t>
+        </is>
+      </c>
+      <c r="H201" s="16" t="inlineStr">
+        <is>
+          <t>마투그로수두술</t>
+        </is>
+      </c>
+      <c r="I201" s="16" t="inlineStr">
+        <is>
+          <t>BR_MatoGrossodoSul</t>
+        </is>
+      </c>
+      <c r="J201" s="16" t="inlineStr">
+        <is>
+          <t>Mato Grosso do Sul; MS (Brazil); 마투그로수두술주</t>
+        </is>
+      </c>
+      <c r="K201" s="16" t="inlineStr">
+        <is>
+          <t>Region</t>
+        </is>
+      </c>
+      <c r="L201" s="16" t="inlineStr">
+        <is>
+          <t>브라질 대두 재배 지역(tier 1) — 생산 비중 확대 중</t>
+        </is>
+      </c>
+      <c r="M201" s="16" t="inlineStr">
+        <is>
+          <t>지역별 기후 신호는 일반화하지 않는다(지역 간 단순 평균 금지 — 재배면적 가중 없이는 합산 불가) · 좌표는 행정 중심이 아닌 주산 벨트 중심(NASA POWER 0.5° 격자 감도) · 라벨 CONFIRMED/INFERENCE는 config coord_status와 동기 · 좌표 이동 시 구좌표 수집분과 시계열을 잇지 않는다(vintage 분리)</t>
+        </is>
+      </c>
+      <c r="N201" s="16" t="inlineStr">
+        <is>
+          <t>Supply</t>
+        </is>
+      </c>
+      <c r="O201" s="16" t="inlineStr">
+        <is>
+          <t>CONTEXT</t>
+        </is>
+      </c>
+      <c r="P201" s="16" t="inlineStr">
+        <is>
+          <t>lat/lon(deg)</t>
+        </is>
+      </c>
+      <c r="Q201" s="16" t="inlineStr">
+        <is>
+          <t>정본 좌표 표 §3.2 기준 — 아카이브 daily 8변수(토양 hourly 포함)+예보 FCST_</t>
+        </is>
+      </c>
+      <c r="R201" s="16" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="S201" s="16" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="T201" s="16" t="inlineStr">
+        <is>
+          <t>ProductionRegion</t>
+        </is>
+      </c>
+      <c r="U201" s="16" t="inlineStr">
+        <is>
+          <t>LOCATED_AT</t>
+        </is>
+      </c>
+      <c r="V201" s="16" t="inlineStr">
+        <is>
+          <t>config/production_regions.yaml,climate_regions_forecast_weathernext_2026_09_13.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="202" ht="42" customHeight="1">
+      <c r="A202" s="16" t="inlineStr">
+        <is>
+          <t>TERM-201</t>
+        </is>
+      </c>
+      <c r="B202" s="16" t="inlineStr">
+        <is>
+          <t>농업·농기상</t>
+        </is>
+      </c>
+      <c r="C202" s="16" t="inlineStr">
+        <is>
+          <t>Agriculture &amp; Agrometeorology</t>
+        </is>
+      </c>
+      <c r="D202" s="16" t="inlineStr">
+        <is>
+          <t>생산지역</t>
+        </is>
+      </c>
+      <c r="E202" s="16" t="inlineStr">
+        <is>
+          <t>Production Regions</t>
+        </is>
+      </c>
+      <c r="F202" s="16" t="inlineStr">
+        <is>
+          <t>생산지역</t>
+        </is>
+      </c>
+      <c r="G202" s="16" t="inlineStr">
+        <is>
+          <t>Córdoba (Argentina)</t>
+        </is>
+      </c>
+      <c r="H202" s="16" t="inlineStr">
+        <is>
+          <t>코르도바</t>
+        </is>
+      </c>
+      <c r="I202" s="16" t="inlineStr">
+        <is>
+          <t>AR_Cordoba</t>
+        </is>
+      </c>
+      <c r="J202" s="16" t="inlineStr">
+        <is>
+          <t>Cordoba Province; 코르도바주</t>
+        </is>
+      </c>
+      <c r="K202" s="16" t="inlineStr">
+        <is>
+          <t>Region</t>
+        </is>
+      </c>
+      <c r="L202" s="16" t="inlineStr">
+        <is>
+          <t>아르헨티나 대두 재배 지역(tier 1) — 아르헨티나 재배 1위 주</t>
+        </is>
+      </c>
+      <c r="M202" s="16" t="inlineStr">
+        <is>
+          <t>지역별 기후 신호는 일반화하지 않는다(지역 간 단순 평균 금지 — 재배면적 가중 없이는 합산 불가) · 좌표는 행정 중심이 아닌 주산 벨트 중심(NASA POWER 0.5° 격자 감도) · 라벨 CONFIRMED/INFERENCE는 config coord_status와 동기 · 좌표 이동 시 구좌표 수집분과 시계열을 잇지 않는다(vintage 분리)</t>
+        </is>
+      </c>
+      <c r="N202" s="16" t="inlineStr">
+        <is>
+          <t>Supply</t>
+        </is>
+      </c>
+      <c r="O202" s="16" t="inlineStr">
+        <is>
+          <t>CONTEXT</t>
+        </is>
+      </c>
+      <c r="P202" s="16" t="inlineStr">
+        <is>
+          <t>lat/lon(deg)</t>
+        </is>
+      </c>
+      <c r="Q202" s="16" t="inlineStr">
+        <is>
+          <t>정본 좌표 표 §3.2 기준 — 아카이브 daily 8변수(토양 hourly 포함)+예보 FCST_</t>
+        </is>
+      </c>
+      <c r="R202" s="16" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="S202" s="16" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="T202" s="16" t="inlineStr">
+        <is>
+          <t>ProductionRegion</t>
+        </is>
+      </c>
+      <c r="U202" s="16" t="inlineStr">
+        <is>
+          <t>LOCATED_AT</t>
+        </is>
+      </c>
+      <c r="V202" s="16" t="inlineStr">
+        <is>
+          <t>config/production_regions.yaml,climate_regions_forecast_weathernext_2026_09_13.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="203" ht="42" customHeight="1">
+      <c r="A203" s="16" t="inlineStr">
+        <is>
+          <t>TERM-202</t>
+        </is>
+      </c>
+      <c r="B203" s="16" t="inlineStr">
+        <is>
+          <t>농업·농기상</t>
+        </is>
+      </c>
+      <c r="C203" s="16" t="inlineStr">
+        <is>
+          <t>Agriculture &amp; Agrometeorology</t>
+        </is>
+      </c>
+      <c r="D203" s="16" t="inlineStr">
+        <is>
+          <t>생산지역</t>
+        </is>
+      </c>
+      <c r="E203" s="16" t="inlineStr">
+        <is>
+          <t>Production Regions</t>
+        </is>
+      </c>
+      <c r="F203" s="16" t="inlineStr">
+        <is>
+          <t>생산지역</t>
+        </is>
+      </c>
+      <c r="G203" s="16" t="inlineStr">
+        <is>
+          <t>Santa Fe (Argentina)</t>
+        </is>
+      </c>
+      <c r="H203" s="16" t="inlineStr">
+        <is>
+          <t>산타페</t>
+        </is>
+      </c>
+      <c r="I203" s="16" t="inlineStr">
+        <is>
+          <t>AR_SantaFe</t>
+        </is>
+      </c>
+      <c r="J203" s="16" t="inlineStr">
+        <is>
+          <t>Santa Fe Province; Rosario crushing hub; 산타페주</t>
+        </is>
+      </c>
+      <c r="K203" s="16" t="inlineStr">
+        <is>
+          <t>Region</t>
+        </is>
+      </c>
+      <c r="L203" s="16" t="inlineStr">
+        <is>
+          <t>아르헨티나 대두 압착 지역(tier 1) — 로사리오 압착 허브(전국 설비 약 80%)</t>
+        </is>
+      </c>
+      <c r="M203" s="16" t="inlineStr">
+        <is>
+          <t>지역별 기후 신호는 일반화하지 않는다(지역 간 단순 평균 금지 — 재배면적 가중 없이는 합산 불가) · 좌표는 행정 중심이 아닌 주산 벨트 중심(NASA POWER 0.5° 격자 감도) · 라벨 CONFIRMED/INFERENCE는 config coord_status와 동기 · 좌표 이동 시 구좌표 수집분과 시계열을 잇지 않는다(vintage 분리)</t>
+        </is>
+      </c>
+      <c r="N203" s="16" t="inlineStr">
+        <is>
+          <t>Supply</t>
+        </is>
+      </c>
+      <c r="O203" s="16" t="inlineStr">
+        <is>
+          <t>CONTEXT</t>
+        </is>
+      </c>
+      <c r="P203" s="16" t="inlineStr">
+        <is>
+          <t>lat/lon(deg)</t>
+        </is>
+      </c>
+      <c r="Q203" s="16" t="inlineStr">
+        <is>
+          <t>정본 좌표 표 §3.2 기준 — 아카이브 daily 8변수(토양 hourly 포함)+예보 FCST_</t>
+        </is>
+      </c>
+      <c r="R203" s="16" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="S203" s="16" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="T203" s="16" t="inlineStr">
+        <is>
+          <t>ProductionRegion</t>
+        </is>
+      </c>
+      <c r="U203" s="16" t="inlineStr">
+        <is>
+          <t>LOCATED_AT</t>
+        </is>
+      </c>
+      <c r="V203" s="16" t="inlineStr">
+        <is>
+          <t>config/production_regions.yaml,climate_regions_forecast_weathernext_2026_09_13.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="204" ht="42" customHeight="1">
+      <c r="A204" s="16" t="inlineStr">
+        <is>
+          <t>TERM-203</t>
+        </is>
+      </c>
+      <c r="B204" s="16" t="inlineStr">
+        <is>
+          <t>농업·농기상</t>
+        </is>
+      </c>
+      <c r="C204" s="16" t="inlineStr">
+        <is>
+          <t>Agriculture &amp; Agrometeorology</t>
+        </is>
+      </c>
+      <c r="D204" s="16" t="inlineStr">
+        <is>
+          <t>생산지역</t>
+        </is>
+      </c>
+      <c r="E204" s="16" t="inlineStr">
+        <is>
+          <t>Production Regions</t>
+        </is>
+      </c>
+      <c r="F204" s="16" t="inlineStr">
+        <is>
+          <t>생산지역</t>
+        </is>
+      </c>
+      <c r="G204" s="16" t="inlineStr">
+        <is>
+          <t>Buenos Aires Province (Argentina)</t>
+        </is>
+      </c>
+      <c r="H204" s="16" t="inlineStr">
+        <is>
+          <t>부에노스아이레스</t>
+        </is>
+      </c>
+      <c r="I204" s="16" t="inlineStr">
+        <is>
+          <t>AR_BuenosAires</t>
+        </is>
+      </c>
+      <c r="J204" s="16" t="inlineStr">
+        <is>
+          <t>Buenos Aires; 부에노스아이레스주</t>
+        </is>
+      </c>
+      <c r="K204" s="16" t="inlineStr">
+        <is>
+          <t>Region</t>
+        </is>
+      </c>
+      <c r="L204" s="16" t="inlineStr">
+        <is>
+          <t>아르헨티나 대두 재배 지역(tier 1) — 팜파스 핵심 재배 지역</t>
+        </is>
+      </c>
+      <c r="M204" s="16" t="inlineStr">
+        <is>
+          <t>지역별 기후 신호는 일반화하지 않는다(지역 간 단순 평균 금지 — 재배면적 가중 없이는 합산 불가) · 좌표는 행정 중심이 아닌 주산 벨트 중심(NASA POWER 0.5° 격자 감도) · 라벨 CONFIRMED/INFERENCE는 config coord_status와 동기 · 좌표 이동 시 구좌표 수집분과 시계열을 잇지 않는다(vintage 분리)</t>
+        </is>
+      </c>
+      <c r="N204" s="16" t="inlineStr">
+        <is>
+          <t>Supply</t>
+        </is>
+      </c>
+      <c r="O204" s="16" t="inlineStr">
+        <is>
+          <t>CONTEXT</t>
+        </is>
+      </c>
+      <c r="P204" s="16" t="inlineStr">
+        <is>
+          <t>lat/lon(deg)</t>
+        </is>
+      </c>
+      <c r="Q204" s="16" t="inlineStr">
+        <is>
+          <t>정본 좌표 표 §3.2 기준 — 아카이브 daily 8변수(토양 hourly 포함)+예보 FCST_</t>
+        </is>
+      </c>
+      <c r="R204" s="16" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="S204" s="16" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="T204" s="16" t="inlineStr">
+        <is>
+          <t>ProductionRegion</t>
+        </is>
+      </c>
+      <c r="U204" s="16" t="inlineStr">
+        <is>
+          <t>LOCATED_AT</t>
+        </is>
+      </c>
+      <c r="V204" s="16" t="inlineStr">
+        <is>
+          <t>config/production_regions.yaml,climate_regions_forecast_weathernext_2026_09_13.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="205" ht="42" customHeight="1">
+      <c r="A205" s="16" t="inlineStr">
+        <is>
+          <t>TERM-204</t>
+        </is>
+      </c>
+      <c r="B205" s="16" t="inlineStr">
+        <is>
+          <t>농업·농기상</t>
+        </is>
+      </c>
+      <c r="C205" s="16" t="inlineStr">
+        <is>
+          <t>Agriculture &amp; Agrometeorology</t>
+        </is>
+      </c>
+      <c r="D205" s="16" t="inlineStr">
+        <is>
+          <t>생산지역</t>
+        </is>
+      </c>
+      <c r="E205" s="16" t="inlineStr">
+        <is>
+          <t>Production Regions</t>
+        </is>
+      </c>
+      <c r="F205" s="16" t="inlineStr">
+        <is>
+          <t>생산지역</t>
+        </is>
+      </c>
+      <c r="G205" s="16" t="inlineStr">
+        <is>
+          <t>Rio Grande do Sul (Brazil)</t>
+        </is>
+      </c>
+      <c r="H205" s="16" t="inlineStr">
+        <is>
+          <t>히우그란지두술</t>
+        </is>
+      </c>
+      <c r="I205" s="16" t="inlineStr">
+        <is>
+          <t>BR_RioGrandedoSul</t>
+        </is>
+      </c>
+      <c r="J205" s="16" t="inlineStr">
+        <is>
+          <t>Rio Grande do Sul; RS (Brazil); 히우그란지두술주; Cruz Alta belt</t>
+        </is>
+      </c>
+      <c r="K205" s="16" t="inlineStr">
+        <is>
+          <t>Region</t>
+        </is>
+      </c>
+      <c r="L205" s="16" t="inlineStr">
+        <is>
+          <t>브라질 대두 재배 지역(tier 2) — 브라질 대두 생산 4위 주 · 약 18.6백만 t(전국 171.5백만 t의 약 11%, CONAB 2024/25) · 남부 최대 가뭄 손실 지역(Embrapa 50년 정량)</t>
+        </is>
+      </c>
+      <c r="M205" s="16" t="inlineStr">
+        <is>
+          <t>지역별 기후 신호는 일반화하지 않는다(지역 간 단순 평균 금지 — 재배면적 가중 없이는 합산 불가) · 좌표는 행정 중심이 아닌 주산 벨트 중심(NASA POWER 0.5° 격자 감도) · 라벨 CONFIRMED/INFERENCE는 config coord_status와 동기 · 좌표 이동 시 구좌표 수집분과 시계열을 잇지 않는다(vintage 분리)</t>
+        </is>
+      </c>
+      <c r="N205" s="16" t="inlineStr">
+        <is>
+          <t>Supply</t>
+        </is>
+      </c>
+      <c r="O205" s="16" t="inlineStr">
+        <is>
+          <t>CONTEXT</t>
+        </is>
+      </c>
+      <c r="P205" s="16" t="inlineStr">
+        <is>
+          <t>lat/lon(deg)</t>
+        </is>
+      </c>
+      <c r="Q205" s="16" t="inlineStr">
+        <is>
+          <t>climate_regions_forecast_weathernext_2026_09_13.md §2 기준 — daily 6변수+예보, 모델 투입은 정본 편입 후</t>
+        </is>
+      </c>
+      <c r="R205" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="S205" s="16" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="T205" s="16" t="inlineStr">
+        <is>
+          <t>ProductionRegion</t>
+        </is>
+      </c>
+      <c r="U205" s="16" t="inlineStr">
+        <is>
+          <t>LOCATED_AT</t>
+        </is>
+      </c>
+      <c r="V205" s="16" t="inlineStr">
+        <is>
+          <t>config/production_regions.yaml,climate_regions_forecast_weathernext_2026_09_13.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="206" ht="42" customHeight="1">
+      <c r="A206" s="16" t="inlineStr">
+        <is>
+          <t>TERM-205</t>
+        </is>
+      </c>
+      <c r="B206" s="16" t="inlineStr">
+        <is>
+          <t>농업·농기상</t>
+        </is>
+      </c>
+      <c r="C206" s="16" t="inlineStr">
+        <is>
+          <t>Agriculture &amp; Agrometeorology</t>
+        </is>
+      </c>
+      <c r="D206" s="16" t="inlineStr">
+        <is>
+          <t>생산지역</t>
+        </is>
+      </c>
+      <c r="E206" s="16" t="inlineStr">
+        <is>
+          <t>Production Regions</t>
+        </is>
+      </c>
+      <c r="F206" s="16" t="inlineStr">
+        <is>
+          <t>생산지역</t>
+        </is>
+      </c>
+      <c r="G206" s="16" t="inlineStr">
+        <is>
+          <t>Goiás (Brazil)</t>
+        </is>
+      </c>
+      <c r="H206" s="16" t="inlineStr">
+        <is>
+          <t>고이아스</t>
+        </is>
+      </c>
+      <c r="I206" s="16" t="inlineStr">
+        <is>
+          <t>BR_Goias</t>
+        </is>
+      </c>
+      <c r="J206" s="16" t="inlineStr">
+        <is>
+          <t>Goias; GO (Brazil); 고이아스주; Rio Verde belt</t>
+        </is>
+      </c>
+      <c r="K206" s="16" t="inlineStr">
+        <is>
+          <t>Region</t>
+        </is>
+      </c>
+      <c r="L206" s="16" t="inlineStr">
+        <is>
+          <t>브라질 대두 재배 지역(tier 2) — 브라질 대두 생산 3위 주 · 약 20.4백만 t(전국의 약 12%, CONAB 2024/25 · 단수 4,183 kg/ha 전국 최고) · 세하두 남서부 Rio Verde·Jataí·Cristalina가 생산액 상위</t>
+        </is>
+      </c>
+      <c r="M206" s="16" t="inlineStr">
+        <is>
+          <t>지역별 기후 신호는 일반화하지 않는다(지역 간 단순 평균 금지 — 재배면적 가중 없이는 합산 불가) · 좌표는 행정 중심이 아닌 주산 벨트 중심(NASA POWER 0.5° 격자 감도) · 라벨 CONFIRMED/INFERENCE는 config coord_status와 동기 · 좌표 이동 시 구좌표 수집분과 시계열을 잇지 않는다(vintage 분리)</t>
+        </is>
+      </c>
+      <c r="N206" s="16" t="inlineStr">
+        <is>
+          <t>Supply</t>
+        </is>
+      </c>
+      <c r="O206" s="16" t="inlineStr">
+        <is>
+          <t>CONTEXT</t>
+        </is>
+      </c>
+      <c r="P206" s="16" t="inlineStr">
+        <is>
+          <t>lat/lon(deg)</t>
+        </is>
+      </c>
+      <c r="Q206" s="16" t="inlineStr">
+        <is>
+          <t>climate_regions_forecast_weathernext_2026_09_13.md §2 기준 — daily 6변수+예보, 모델 투입은 정본 편입 후</t>
+        </is>
+      </c>
+      <c r="R206" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="S206" s="16" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="T206" s="16" t="inlineStr">
+        <is>
+          <t>ProductionRegion</t>
+        </is>
+      </c>
+      <c r="U206" s="16" t="inlineStr">
+        <is>
+          <t>LOCATED_AT</t>
+        </is>
+      </c>
+      <c r="V206" s="16" t="inlineStr">
+        <is>
+          <t>config/production_regions.yaml,climate_regions_forecast_weathernext_2026_09_13.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="207" ht="42" customHeight="1">
+      <c r="A207" s="16" t="inlineStr">
+        <is>
+          <t>TERM-206</t>
+        </is>
+      </c>
+      <c r="B207" s="16" t="inlineStr">
+        <is>
+          <t>농업·농기상</t>
+        </is>
+      </c>
+      <c r="C207" s="16" t="inlineStr">
+        <is>
+          <t>Agriculture &amp; Agrometeorology</t>
+        </is>
+      </c>
+      <c r="D207" s="16" t="inlineStr">
+        <is>
+          <t>생산지역</t>
+        </is>
+      </c>
+      <c r="E207" s="16" t="inlineStr">
+        <is>
+          <t>Production Regions</t>
+        </is>
+      </c>
+      <c r="F207" s="16" t="inlineStr">
+        <is>
+          <t>생산지역</t>
+        </is>
+      </c>
+      <c r="G207" s="16" t="inlineStr">
+        <is>
+          <t>Minnesota (USA)</t>
+        </is>
+      </c>
+      <c r="H207" s="16" t="inlineStr">
+        <is>
+          <t>미네소타</t>
+        </is>
+      </c>
+      <c r="I207" s="16" t="inlineStr">
+        <is>
+          <t>US_Minnesota</t>
+        </is>
+      </c>
+      <c r="J207" s="16" t="inlineStr">
+        <is>
+          <t>Minnesota; MN; 미네소타주</t>
+        </is>
+      </c>
+      <c r="K207" s="16" t="inlineStr">
+        <is>
+          <t>Region</t>
+        </is>
+      </c>
+      <c r="L207" s="16" t="inlineStr">
+        <is>
+          <t>미국 대두 재배 지역(tier 2) — 미국 대두 생산 3위 주 · 349.4백만 bu(전국 4,366백만 bu의 8.0%, USDA NASS 2024 Crop Production Summary) · 상위 카운티 Redwood·Renville·Blue Earth·Jackson(남서·남중부)</t>
+        </is>
+      </c>
+      <c r="M207" s="16" t="inlineStr">
+        <is>
+          <t>지역별 기후 신호는 일반화하지 않는다(지역 간 단순 평균 금지 — 재배면적 가중 없이는 합산 불가) · 좌표는 행정 중심이 아닌 주산 벨트 중심(NASA POWER 0.5° 격자 감도) · 라벨 CONFIRMED/INFERENCE는 config coord_status와 동기 · 좌표 이동 시 구좌표 수집분과 시계열을 잇지 않는다(vintage 분리)</t>
+        </is>
+      </c>
+      <c r="N207" s="16" t="inlineStr">
+        <is>
+          <t>Supply</t>
+        </is>
+      </c>
+      <c r="O207" s="16" t="inlineStr">
+        <is>
+          <t>CONTEXT</t>
+        </is>
+      </c>
+      <c r="P207" s="16" t="inlineStr">
+        <is>
+          <t>lat/lon(deg)</t>
+        </is>
+      </c>
+      <c r="Q207" s="16" t="inlineStr">
+        <is>
+          <t>climate_regions_forecast_weathernext_2026_09_13.md §2 기준 — daily 6변수+예보, 모델 투입은 정본 편입 후</t>
+        </is>
+      </c>
+      <c r="R207" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="S207" s="16" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="T207" s="16" t="inlineStr">
+        <is>
+          <t>ProductionRegion</t>
+        </is>
+      </c>
+      <c r="U207" s="16" t="inlineStr">
+        <is>
+          <t>LOCATED_AT</t>
+        </is>
+      </c>
+      <c r="V207" s="16" t="inlineStr">
+        <is>
+          <t>config/production_regions.yaml,climate_regions_forecast_weathernext_2026_09_13.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="208" ht="42" customHeight="1">
+      <c r="A208" s="16" t="inlineStr">
+        <is>
+          <t>TERM-207</t>
+        </is>
+      </c>
+      <c r="B208" s="16" t="inlineStr">
+        <is>
+          <t>농업·농기상</t>
+        </is>
+      </c>
+      <c r="C208" s="16" t="inlineStr">
+        <is>
+          <t>Agriculture &amp; Agrometeorology</t>
+        </is>
+      </c>
+      <c r="D208" s="16" t="inlineStr">
+        <is>
+          <t>생산지역</t>
+        </is>
+      </c>
+      <c r="E208" s="16" t="inlineStr">
+        <is>
+          <t>Production Regions</t>
+        </is>
+      </c>
+      <c r="F208" s="16" t="inlineStr">
+        <is>
+          <t>생산지역</t>
+        </is>
+      </c>
+      <c r="G208" s="16" t="inlineStr">
+        <is>
+          <t>Nebraska (USA)</t>
+        </is>
+      </c>
+      <c r="H208" s="16" t="inlineStr">
+        <is>
+          <t>네브래스카</t>
+        </is>
+      </c>
+      <c r="I208" s="16" t="inlineStr">
+        <is>
+          <t>US_Nebraska</t>
+        </is>
+      </c>
+      <c r="J208" s="16" t="inlineStr">
+        <is>
+          <t>Nebraska; NE; 네브래스카주</t>
+        </is>
+      </c>
+      <c r="K208" s="16" t="inlineStr">
+        <is>
+          <t>Region</t>
+        </is>
+      </c>
+      <c r="L208" s="16" t="inlineStr">
+        <is>
+          <t>미국 대두 재배 지역(tier 2) — 미국 대두 생산 5위 주 · 301.0백만 bu(전국의 6.9%, USDA NASS 네브래스카 2024 연간 요약 · 단수 57.5 bu/ac 기록) · 동부·플랫강 유역 집중(Saunders·York·Fillmore) · 관개 비중 높음</t>
+        </is>
+      </c>
+      <c r="M208" s="16" t="inlineStr">
+        <is>
+          <t>지역별 기후 신호는 일반화하지 않는다(지역 간 단순 평균 금지 — 재배면적 가중 없이는 합산 불가) · 좌표는 행정 중심이 아닌 주산 벨트 중심(NASA POWER 0.5° 격자 감도) · 라벨 CONFIRMED/INFERENCE는 config coord_status와 동기 · 좌표 이동 시 구좌표 수집분과 시계열을 잇지 않는다(vintage 분리)</t>
+        </is>
+      </c>
+      <c r="N208" s="16" t="inlineStr">
+        <is>
+          <t>Supply</t>
+        </is>
+      </c>
+      <c r="O208" s="16" t="inlineStr">
+        <is>
+          <t>CONTEXT</t>
+        </is>
+      </c>
+      <c r="P208" s="16" t="inlineStr">
+        <is>
+          <t>lat/lon(deg)</t>
+        </is>
+      </c>
+      <c r="Q208" s="16" t="inlineStr">
+        <is>
+          <t>climate_regions_forecast_weathernext_2026_09_13.md §2 기준 — daily 6변수+예보, 모델 투입은 정본 편입 후</t>
+        </is>
+      </c>
+      <c r="R208" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="S208" s="16" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="T208" s="16" t="inlineStr">
+        <is>
+          <t>ProductionRegion</t>
+        </is>
+      </c>
+      <c r="U208" s="16" t="inlineStr">
+        <is>
+          <t>LOCATED_AT</t>
+        </is>
+      </c>
+      <c r="V208" s="16" t="inlineStr">
+        <is>
+          <t>config/production_regions.yaml,climate_regions_forecast_weathernext_2026_09_13.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="209" ht="42" customHeight="1">
+      <c r="A209" s="16" t="inlineStr">
+        <is>
+          <t>TERM-208</t>
+        </is>
+      </c>
+      <c r="B209" s="16" t="inlineStr">
+        <is>
+          <t>농업·농기상</t>
+        </is>
+      </c>
+      <c r="C209" s="16" t="inlineStr">
+        <is>
+          <t>Agriculture &amp; Agrometeorology</t>
+        </is>
+      </c>
+      <c r="D209" s="16" t="inlineStr">
+        <is>
+          <t>생산지역</t>
+        </is>
+      </c>
+      <c r="E209" s="16" t="inlineStr">
+        <is>
+          <t>Production Regions</t>
+        </is>
+      </c>
+      <c r="F209" s="16" t="inlineStr">
+        <is>
+          <t>생산지역</t>
+        </is>
+      </c>
+      <c r="G209" s="16" t="inlineStr">
+        <is>
+          <t>Ohio (USA)</t>
+        </is>
+      </c>
+      <c r="H209" s="16" t="inlineStr">
+        <is>
+          <t>오하이오</t>
+        </is>
+      </c>
+      <c r="I209" s="16" t="inlineStr">
+        <is>
+          <t>US_Ohio</t>
+        </is>
+      </c>
+      <c r="J209" s="16" t="inlineStr">
+        <is>
+          <t>Ohio; OH; 오하이오주</t>
+        </is>
+      </c>
+      <c r="K209" s="16" t="inlineStr">
+        <is>
+          <t>Region</t>
+        </is>
+      </c>
+      <c r="L209" s="16" t="inlineStr">
+        <is>
+          <t>미국 대두 재배 지역(tier 2) — 미국 대두 생산 6위 주 · 274.3백만 bu(전국의 6.3%, USDA NASS 2024) · 상위 카운티 Wood·Darke·Seneca(서부·북서부)</t>
+        </is>
+      </c>
+      <c r="M209" s="16" t="inlineStr">
+        <is>
+          <t>지역별 기후 신호는 일반화하지 않는다(지역 간 단순 평균 금지 — 재배면적 가중 없이는 합산 불가) · 좌표는 행정 중심이 아닌 주산 벨트 중심(NASA POWER 0.5° 격자 감도) · 라벨 CONFIRMED/INFERENCE는 config coord_status와 동기 · 좌표 이동 시 구좌표 수집분과 시계열을 잇지 않는다(vintage 분리)</t>
+        </is>
+      </c>
+      <c r="N209" s="16" t="inlineStr">
+        <is>
+          <t>Supply</t>
+        </is>
+      </c>
+      <c r="O209" s="16" t="inlineStr">
+        <is>
+          <t>CONTEXT</t>
+        </is>
+      </c>
+      <c r="P209" s="16" t="inlineStr">
+        <is>
+          <t>lat/lon(deg)</t>
+        </is>
+      </c>
+      <c r="Q209" s="16" t="inlineStr">
+        <is>
+          <t>climate_regions_forecast_weathernext_2026_09_13.md §2 기준 — daily 6변수+예보, 모델 투입은 정본 편입 후</t>
+        </is>
+      </c>
+      <c r="R209" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="S209" s="16" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="T209" s="16" t="inlineStr">
+        <is>
+          <t>ProductionRegion</t>
+        </is>
+      </c>
+      <c r="U209" s="16" t="inlineStr">
+        <is>
+          <t>LOCATED_AT</t>
+        </is>
+      </c>
+      <c r="V209" s="16" t="inlineStr">
+        <is>
+          <t>config/production_regions.yaml,climate_regions_forecast_weathernext_2026_09_13.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="210" ht="42" customHeight="1">
+      <c r="A210" s="16" t="inlineStr">
+        <is>
+          <t>TERM-209</t>
+        </is>
+      </c>
+      <c r="B210" s="16" t="inlineStr">
+        <is>
+          <t>농업·농기상</t>
+        </is>
+      </c>
+      <c r="C210" s="16" t="inlineStr">
+        <is>
+          <t>Agriculture &amp; Agrometeorology</t>
+        </is>
+      </c>
+      <c r="D210" s="16" t="inlineStr">
+        <is>
+          <t>생산지역</t>
+        </is>
+      </c>
+      <c r="E210" s="16" t="inlineStr">
+        <is>
+          <t>Production Regions</t>
+        </is>
+      </c>
+      <c r="F210" s="16" t="inlineStr">
+        <is>
+          <t>생산지역</t>
+        </is>
+      </c>
+      <c r="G210" s="16" t="inlineStr">
+        <is>
+          <t>Alto Paraná (Paraguay)</t>
+        </is>
+      </c>
+      <c r="H210" s="16" t="inlineStr">
+        <is>
+          <t>알토파라나(파라과이)</t>
+        </is>
+      </c>
+      <c r="I210" s="16" t="inlineStr">
+        <is>
+          <t>PY_AltoParana</t>
+        </is>
+      </c>
+      <c r="J210" s="16" t="inlineStr">
+        <is>
+          <t>Alto Parana Department; 알토파라나도; Santa Rita belt</t>
+        </is>
+      </c>
+      <c r="K210" s="16" t="inlineStr">
+        <is>
+          <t>Region</t>
+        </is>
+      </c>
+      <c r="L210" s="16" t="inlineStr">
+        <is>
+          <t>파라과이 대두 재배 지역(tier 2) — 파라과이 대두 생산 1위 도 · 3.06백만 t(전국 9.34백만 t의 32.7%, MAG·INBIO 2024/25) · 파종 면적 896천 ha(26.3%, CAPECO 2025/26)</t>
+        </is>
+      </c>
+      <c r="M210" s="16" t="inlineStr">
+        <is>
+          <t>지역별 기후 신호는 일반화하지 않는다(지역 간 단순 평균 금지 — 재배면적 가중 없이는 합산 불가) · 좌표는 행정 중심이 아닌 주산 벨트 중심(NASA POWER 0.5° 격자 감도) · 라벨 CONFIRMED/INFERENCE는 config coord_status와 동기 · 좌표 이동 시 구좌표 수집분과 시계열을 잇지 않는다(vintage 분리)</t>
+        </is>
+      </c>
+      <c r="N210" s="16" t="inlineStr">
+        <is>
+          <t>Supply</t>
+        </is>
+      </c>
+      <c r="O210" s="16" t="inlineStr">
+        <is>
+          <t>CONTEXT</t>
+        </is>
+      </c>
+      <c r="P210" s="16" t="inlineStr">
+        <is>
+          <t>lat/lon(deg)</t>
+        </is>
+      </c>
+      <c r="Q210" s="16" t="inlineStr">
+        <is>
+          <t>climate_regions_forecast_weathernext_2026_09_13.md §2 기준 — daily 6변수+예보, 모델 투입은 정본 편입 후</t>
+        </is>
+      </c>
+      <c r="R210" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="S210" s="16" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="T210" s="16" t="inlineStr">
+        <is>
+          <t>ProductionRegion</t>
+        </is>
+      </c>
+      <c r="U210" s="16" t="inlineStr">
+        <is>
+          <t>LOCATED_AT</t>
+        </is>
+      </c>
+      <c r="V210" s="16" t="inlineStr">
+        <is>
+          <t>config/production_regions.yaml,climate_regions_forecast_weathernext_2026_09_13.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="211" ht="42" customHeight="1">
+      <c r="A211" s="16" t="inlineStr">
+        <is>
+          <t>TERM-210</t>
+        </is>
+      </c>
+      <c r="B211" s="16" t="inlineStr">
+        <is>
+          <t>농업·농기상</t>
+        </is>
+      </c>
+      <c r="C211" s="16" t="inlineStr">
+        <is>
+          <t>Agriculture &amp; Agrometeorology</t>
+        </is>
+      </c>
+      <c r="D211" s="16" t="inlineStr">
+        <is>
+          <t>생산지역</t>
+        </is>
+      </c>
+      <c r="E211" s="16" t="inlineStr">
+        <is>
+          <t>Production Regions</t>
+        </is>
+      </c>
+      <c r="F211" s="16" t="inlineStr">
+        <is>
+          <t>생산지역</t>
+        </is>
+      </c>
+      <c r="G211" s="16" t="inlineStr">
+        <is>
+          <t>Madhya Pradesh (India)</t>
+        </is>
+      </c>
+      <c r="H211" s="16" t="inlineStr">
+        <is>
+          <t>마디아프라데시(인도)</t>
+        </is>
+      </c>
+      <c r="I211" s="16" t="inlineStr">
+        <is>
+          <t>IN_MadhyaPradesh</t>
+        </is>
+      </c>
+      <c r="J211" s="16" t="inlineStr">
+        <is>
+          <t>Madhya Pradesh; MP (India); 마디아프라데시주; Malwa plateau</t>
+        </is>
+      </c>
+      <c r="K211" s="16" t="inlineStr">
+        <is>
+          <t>Region</t>
+        </is>
+      </c>
+      <c r="L211" s="16" t="inlineStr">
+        <is>
+          <t>인도 대두 재배 지역(tier 2) — 인도 대두 생산 1위 주 · 55.4 lakh t(전국 125.8 lakh t의 약 44%, SOPA kharif 2024) · 수입 관세 정책 연계(인도는 GAIN 국가 상위)</t>
+        </is>
+      </c>
+      <c r="M211" s="16" t="inlineStr">
+        <is>
+          <t>지역별 기후 신호는 일반화하지 않는다(지역 간 단순 평균 금지 — 재배면적 가중 없이는 합산 불가) · 좌표는 행정 중심이 아닌 주산 벨트 중심(NASA POWER 0.5° 격자 감도) · 라벨 CONFIRMED/INFERENCE는 config coord_status와 동기 · 좌표 이동 시 구좌표 수집분과 시계열을 잇지 않는다(vintage 분리)</t>
+        </is>
+      </c>
+      <c r="N211" s="16" t="inlineStr">
+        <is>
+          <t>Supply</t>
+        </is>
+      </c>
+      <c r="O211" s="16" t="inlineStr">
+        <is>
+          <t>CONTEXT</t>
+        </is>
+      </c>
+      <c r="P211" s="16" t="inlineStr">
+        <is>
+          <t>lat/lon(deg)</t>
+        </is>
+      </c>
+      <c r="Q211" s="16" t="inlineStr">
+        <is>
+          <t>climate_regions_forecast_weathernext_2026_09_13.md §2 기준 — daily 6변수+예보, 모델 투입은 정본 편입 후</t>
+        </is>
+      </c>
+      <c r="R211" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="S211" s="16" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="T211" s="16" t="inlineStr">
+        <is>
+          <t>ProductionRegion</t>
+        </is>
+      </c>
+      <c r="U211" s="16" t="inlineStr">
+        <is>
+          <t>LOCATED_AT</t>
+        </is>
+      </c>
+      <c r="V211" s="16" t="inlineStr">
+        <is>
+          <t>config/production_regions.yaml,climate_regions_forecast_weathernext_2026_09_13.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="212" ht="42" customHeight="1">
+      <c r="A212" s="16" t="inlineStr">
+        <is>
+          <t>TERM-211</t>
+        </is>
+      </c>
+      <c r="B212" s="16" t="inlineStr">
+        <is>
+          <t>농업·농기상</t>
+        </is>
+      </c>
+      <c r="C212" s="16" t="inlineStr">
+        <is>
+          <t>Agriculture &amp; Agrometeorology</t>
+        </is>
+      </c>
+      <c r="D212" s="16" t="inlineStr">
+        <is>
+          <t>생산지역</t>
+        </is>
+      </c>
+      <c r="E212" s="16" t="inlineStr">
+        <is>
+          <t>Production Regions</t>
+        </is>
+      </c>
+      <c r="F212" s="16" t="inlineStr">
+        <is>
+          <t>생산지역</t>
+        </is>
+      </c>
+      <c r="G212" s="16" t="inlineStr">
+        <is>
+          <t>Sabah (Malaysia)</t>
+        </is>
+      </c>
+      <c r="H212" s="16" t="inlineStr">
+        <is>
+          <t>사바(말레이시아)</t>
+        </is>
+      </c>
+      <c r="I212" s="16" t="inlineStr">
+        <is>
+          <t>MY_Sabah</t>
+        </is>
+      </c>
+      <c r="J212" s="16" t="inlineStr">
+        <is>
+          <t>Sabah; 사바주; Lahad Datu-Tawau belt</t>
+        </is>
+      </c>
+      <c r="K212" s="16" t="inlineStr">
+        <is>
+          <t>Region</t>
+        </is>
+      </c>
+      <c r="L212" s="16" t="inlineStr">
+        <is>
+          <t>말레이시아 팜 재배 지역(tier 2) — 말레이시아 CPO 생산 1위 주 · 4.27백만 t(전국 19.34백만 t의 22.1%, MPIC·MPOB 2024) · 식재 면적 약 1.48백만 ha(26.4%) · 동해안 Tawau·Lahad Datu·Kinabatangan 등이 주 생산의 약 75%</t>
+        </is>
+      </c>
+      <c r="M212" s="16" t="inlineStr">
+        <is>
+          <t>지역별 기후 신호는 일반화하지 않는다(지역 간 단순 평균 금지 — 재배면적 가중 없이는 합산 불가) · 좌표는 행정 중심이 아닌 주산 벨트 중심(NASA POWER 0.5° 격자 감도) · 라벨 CONFIRMED/INFERENCE는 config coord_status와 동기 · 좌표 이동 시 구좌표 수집분과 시계열을 잇지 않는다(vintage 분리) · 팜 산지 기후는 대두유 가격의 직접 동인이 아니라 대두유−팜유 가격 차이(CE-015) 레짐 판별 보조 입력</t>
+        </is>
+      </c>
+      <c r="N212" s="16" t="inlineStr">
+        <is>
+          <t>Supply</t>
+        </is>
+      </c>
+      <c r="O212" s="16" t="inlineStr">
+        <is>
+          <t>CONTEXT</t>
+        </is>
+      </c>
+      <c r="P212" s="16" t="inlineStr">
+        <is>
+          <t>lat/lon(deg)</t>
+        </is>
+      </c>
+      <c r="Q212" s="16" t="inlineStr">
+        <is>
+          <t>climate_regions_forecast_weathernext_2026_09_13.md §2 기준 — daily 6변수+예보, 모델 투입은 정본 편입 후</t>
+        </is>
+      </c>
+      <c r="R212" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="S212" s="16" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="T212" s="16" t="inlineStr">
+        <is>
+          <t>ProductionRegion</t>
+        </is>
+      </c>
+      <c r="U212" s="16" t="inlineStr">
+        <is>
+          <t>LOCATED_AT</t>
+        </is>
+      </c>
+      <c r="V212" s="16" t="inlineStr">
+        <is>
+          <t>config/production_regions.yaml,climate_regions_forecast_weathernext_2026_09_13.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="213" ht="42" customHeight="1">
+      <c r="A213" s="16" t="inlineStr">
+        <is>
+          <t>TERM-212</t>
+        </is>
+      </c>
+      <c r="B213" s="16" t="inlineStr">
+        <is>
+          <t>농업·농기상</t>
+        </is>
+      </c>
+      <c r="C213" s="16" t="inlineStr">
+        <is>
+          <t>Agriculture &amp; Agrometeorology</t>
+        </is>
+      </c>
+      <c r="D213" s="16" t="inlineStr">
+        <is>
+          <t>생산지역</t>
+        </is>
+      </c>
+      <c r="E213" s="16" t="inlineStr">
+        <is>
+          <t>Production Regions</t>
+        </is>
+      </c>
+      <c r="F213" s="16" t="inlineStr">
+        <is>
+          <t>생산지역</t>
+        </is>
+      </c>
+      <c r="G213" s="16" t="inlineStr">
+        <is>
+          <t>Johor (Malaysia)</t>
+        </is>
+      </c>
+      <c r="H213" s="16" t="inlineStr">
+        <is>
+          <t>조호르</t>
+        </is>
+      </c>
+      <c r="I213" s="16" t="inlineStr">
+        <is>
+          <t>MY_Johor</t>
+        </is>
+      </c>
+      <c r="J213" s="16" t="inlineStr">
+        <is>
+          <t>Johor; 조호르주; Kluang-Kota Tinggi belt</t>
+        </is>
+      </c>
+      <c r="K213" s="16" t="inlineStr">
+        <is>
+          <t>Region</t>
+        </is>
+      </c>
+      <c r="L213" s="16" t="inlineStr">
+        <is>
+          <t>말레이시아 팜 재배 지역(tier 2) — 반도 말레이시아 팜 식재 면적 1위 주 · 659,820 ha(전국의 11.8%, MPOB 2024 Oil Palm Planted Area) · Kluang·Kota Tinggi 중심</t>
+        </is>
+      </c>
+      <c r="M213" s="16" t="inlineStr">
+        <is>
+          <t>지역별 기후 신호는 일반화하지 않는다(지역 간 단순 평균 금지 — 재배면적 가중 없이는 합산 불가) · 좌표는 행정 중심이 아닌 주산 벨트 중심(NASA POWER 0.5° 격자 감도) · 라벨 CONFIRMED/INFERENCE는 config coord_status와 동기 · 좌표 이동 시 구좌표 수집분과 시계열을 잇지 않는다(vintage 분리) · 팜 산지 기후는 대두유 가격의 직접 동인이 아니라 대두유−팜유 가격 차이(CE-015) 레짐 판별 보조 입력</t>
+        </is>
+      </c>
+      <c r="N213" s="16" t="inlineStr">
+        <is>
+          <t>Supply</t>
+        </is>
+      </c>
+      <c r="O213" s="16" t="inlineStr">
+        <is>
+          <t>CONTEXT</t>
+        </is>
+      </c>
+      <c r="P213" s="16" t="inlineStr">
+        <is>
+          <t>lat/lon(deg)</t>
+        </is>
+      </c>
+      <c r="Q213" s="16" t="inlineStr">
+        <is>
+          <t>climate_regions_forecast_weathernext_2026_09_13.md §2 기준 — daily 6변수+예보, 모델 투입은 정본 편입 후</t>
+        </is>
+      </c>
+      <c r="R213" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="S213" s="16" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="T213" s="16" t="inlineStr">
+        <is>
+          <t>ProductionRegion</t>
+        </is>
+      </c>
+      <c r="U213" s="16" t="inlineStr">
+        <is>
+          <t>LOCATED_AT</t>
+        </is>
+      </c>
+      <c r="V213" s="16" t="inlineStr">
+        <is>
+          <t>config/production_regions.yaml,climate_regions_forecast_weathernext_2026_09_13.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="214" ht="42" customHeight="1">
+      <c r="A214" s="16" t="inlineStr">
+        <is>
+          <t>TERM-213</t>
+        </is>
+      </c>
+      <c r="B214" s="16" t="inlineStr">
+        <is>
+          <t>농업·농기상</t>
+        </is>
+      </c>
+      <c r="C214" s="16" t="inlineStr">
+        <is>
+          <t>Agriculture &amp; Agrometeorology</t>
+        </is>
+      </c>
+      <c r="D214" s="16" t="inlineStr">
+        <is>
+          <t>생산지역</t>
+        </is>
+      </c>
+      <c r="E214" s="16" t="inlineStr">
+        <is>
+          <t>Production Regions</t>
+        </is>
+      </c>
+      <c r="F214" s="16" t="inlineStr">
+        <is>
+          <t>생산지역</t>
+        </is>
+      </c>
+      <c r="G214" s="16" t="inlineStr">
+        <is>
+          <t>Riau (Indonesia)</t>
+        </is>
+      </c>
+      <c r="H214" s="16" t="inlineStr">
+        <is>
+          <t>리아우(인도네시아)</t>
+        </is>
+      </c>
+      <c r="I214" s="16" t="inlineStr">
+        <is>
+          <t>ID_Riau</t>
+        </is>
+      </c>
+      <c r="J214" s="16" t="inlineStr">
+        <is>
+          <t>Riau Province; 리아우주; Pekanbaru belt</t>
+        </is>
+      </c>
+      <c r="K214" s="16" t="inlineStr">
+        <is>
+          <t>Region</t>
+        </is>
+      </c>
+      <c r="L214" s="16" t="inlineStr">
+        <is>
+          <t>인도네시아 팜 재배 지역(tier 2) — 인도네시아 팜유 생산 1위 주 · 8.79백만 t(전국 46.99백만 t의 18.7%, BPS 2023) · 생산 상위 군은 Rokan Hulu·Pelalawan·Kampar·Rokan Hilir로 Pekanbaru 동서 양측에 분포</t>
+        </is>
+      </c>
+      <c r="M214" s="16" t="inlineStr">
+        <is>
+          <t>지역별 기후 신호는 일반화하지 않는다(지역 간 단순 평균 금지 — 재배면적 가중 없이는 합산 불가) · 좌표는 행정 중심이 아닌 주산 벨트 중심(NASA POWER 0.5° 격자 감도) · 라벨 CONFIRMED/INFERENCE는 config coord_status와 동기 · 좌표 이동 시 구좌표 수집분과 시계열을 잇지 않는다(vintage 분리) · 팜 산지 기후는 대두유 가격의 직접 동인이 아니라 대두유−팜유 가격 차이(CE-015) 레짐 판별 보조 입력</t>
+        </is>
+      </c>
+      <c r="N214" s="16" t="inlineStr">
+        <is>
+          <t>Supply</t>
+        </is>
+      </c>
+      <c r="O214" s="16" t="inlineStr">
+        <is>
+          <t>CONTEXT</t>
+        </is>
+      </c>
+      <c r="P214" s="16" t="inlineStr">
+        <is>
+          <t>lat/lon(deg)</t>
+        </is>
+      </c>
+      <c r="Q214" s="16" t="inlineStr">
+        <is>
+          <t>climate_regions_forecast_weathernext_2026_09_13.md §2 기준 — daily 6변수+예보, 모델 투입은 정본 편입 후</t>
+        </is>
+      </c>
+      <c r="R214" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="S214" s="16" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="T214" s="16" t="inlineStr">
+        <is>
+          <t>ProductionRegion</t>
+        </is>
+      </c>
+      <c r="U214" s="16" t="inlineStr">
+        <is>
+          <t>LOCATED_AT</t>
+        </is>
+      </c>
+      <c r="V214" s="16" t="inlineStr">
+        <is>
+          <t>config/production_regions.yaml,climate_regions_forecast_weathernext_2026_09_13.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="215" ht="42" customHeight="1">
+      <c r="A215" s="16" t="inlineStr">
+        <is>
+          <t>TERM-214</t>
+        </is>
+      </c>
+      <c r="B215" s="16" t="inlineStr">
+        <is>
+          <t>농업·농기상</t>
+        </is>
+      </c>
+      <c r="C215" s="16" t="inlineStr">
+        <is>
+          <t>Agriculture &amp; Agrometeorology</t>
+        </is>
+      </c>
+      <c r="D215" s="16" t="inlineStr">
+        <is>
+          <t>생산지역</t>
+        </is>
+      </c>
+      <c r="E215" s="16" t="inlineStr">
+        <is>
+          <t>Production Regions</t>
+        </is>
+      </c>
+      <c r="F215" s="16" t="inlineStr">
+        <is>
+          <t>생산지역</t>
+        </is>
+      </c>
+      <c r="G215" s="16" t="inlineStr">
+        <is>
+          <t>Central Kalimantan (Indonesia)</t>
+        </is>
+      </c>
+      <c r="H215" s="16" t="inlineStr">
+        <is>
+          <t>중부칼리만탄</t>
+        </is>
+      </c>
+      <c r="I215" s="16" t="inlineStr">
+        <is>
+          <t>ID_CentralKalimantan</t>
+        </is>
+      </c>
+      <c r="J215" s="16" t="inlineStr">
+        <is>
+          <t>Kalimantan Tengah; Kalteng; 중부칼리만탄주; Sampit belt</t>
+        </is>
+      </c>
+      <c r="K215" s="16" t="inlineStr">
+        <is>
+          <t>Region</t>
+        </is>
+      </c>
+      <c r="L215" s="16" t="inlineStr">
+        <is>
+          <t>인도네시아 팜 재배 지역(tier 2) — 인도네시아 팜유 생산 2위 주 · 8.55백만 t(전국의 18.2%, BPS 2023) · Kotawaringin Timur가 주 생산의 26.7%(1위)·Seruyan 2위 · MY·ID 합산 세계 팜유 80%+(Zhang 2025)</t>
+        </is>
+      </c>
+      <c r="M215" s="16" t="inlineStr">
+        <is>
+          <t>지역별 기후 신호는 일반화하지 않는다(지역 간 단순 평균 금지 — 재배면적 가중 없이는 합산 불가) · 좌표는 행정 중심이 아닌 주산 벨트 중심(NASA POWER 0.5° 격자 감도) · 라벨 CONFIRMED/INFERENCE는 config coord_status와 동기 · 좌표 이동 시 구좌표 수집분과 시계열을 잇지 않는다(vintage 분리) · 팜 산지 기후는 대두유 가격의 직접 동인이 아니라 대두유−팜유 가격 차이(CE-015) 레짐 판별 보조 입력</t>
+        </is>
+      </c>
+      <c r="N215" s="16" t="inlineStr">
+        <is>
+          <t>Supply</t>
+        </is>
+      </c>
+      <c r="O215" s="16" t="inlineStr">
+        <is>
+          <t>CONTEXT</t>
+        </is>
+      </c>
+      <c r="P215" s="16" t="inlineStr">
+        <is>
+          <t>lat/lon(deg)</t>
+        </is>
+      </c>
+      <c r="Q215" s="16" t="inlineStr">
+        <is>
+          <t>climate_regions_forecast_weathernext_2026_09_13.md §2 기준 — daily 6변수+예보, 모델 투입은 정본 편입 후</t>
+        </is>
+      </c>
+      <c r="R215" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="S215" s="16" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="T215" s="16" t="inlineStr">
+        <is>
+          <t>ProductionRegion</t>
+        </is>
+      </c>
+      <c r="U215" s="16" t="inlineStr">
+        <is>
+          <t>LOCATED_AT</t>
+        </is>
+      </c>
+      <c r="V215" s="16" t="inlineStr">
+        <is>
+          <t>config/production_regions.yaml,climate_regions_forecast_weathernext_2026_09_13.md</t>
         </is>
       </c>
     </row>
@@ -24259,7 +26835,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -25197,6 +27773,54 @@
           <t>저장소 경로: docs/research_desk/2026-09/media_source_fallback_design_2026_09_13.md</t>
         </is>
       </c>
+    </row>
+    <row r="30" ht="44.1" customHeight="1">
+      <c r="A30" s="17" t="inlineStr">
+        <is>
+          <t>config/production_regions.yaml</t>
+        </is>
+      </c>
+      <c r="B30" s="17" t="inlineStr">
+        <is>
+          <t>미등록</t>
+        </is>
+      </c>
+      <c r="C30" s="17" t="inlineStr">
+        <is>
+          <t>config/production_regions.yaml</t>
+        </is>
+      </c>
+      <c r="D30" s="17" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E30" s="17" t="inlineStr"/>
+      <c r="F30" s="17" t="inlineStr"/>
+    </row>
+    <row r="31" ht="44.1" customHeight="1">
+      <c r="A31" s="17" t="inlineStr">
+        <is>
+          <t>climate_regions_forecast_weathernext_2026_09_13.md</t>
+        </is>
+      </c>
+      <c r="B31" s="17" t="inlineStr">
+        <is>
+          <t>미등록</t>
+        </is>
+      </c>
+      <c r="C31" s="17" t="inlineStr">
+        <is>
+          <t>climate_regions_forecast_weathernext_2026_09_13.md</t>
+        </is>
+      </c>
+      <c r="D31" s="17" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E31" s="17" t="inlineStr"/>
+      <c r="F31" s="17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/raw/비정형 분석용_핵심 용어 사전집_v1.0.xlsx
+++ b/data/raw/비정형 분석용_핵심 용어 사전집_v1.0.xlsx
@@ -627,7 +627,7 @@
     <row r="1">
       <c r="A1" s="10" t="inlineStr">
         <is>
-          <t>비정형 데이터 핵심 용어사전 v1.1</t>
+          <t>비정형 데이터 핵심 용어사전 v1.2</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="11" t="inlineStr">
         <is>
-          <t>비정형 PDF 해석 · Semantic Layer · Ontology 공통 통제어휘 | 2026-09-13</t>
+          <t>비정형 PDF 해석 · Semantic Layer · Ontology 공통 통제어휘 | 2026-09-14</t>
         </is>
       </c>
     </row>
@@ -875,7 +875,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V215"/>
+  <dimension ref="A1:V231"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -24554,6 +24554,1798 @@
       <c r="V215" s="16" t="inlineStr">
         <is>
           <t>config/production_regions.yaml,climate_regions_forecast_weathernext_2026_09_13.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="216" ht="42" customHeight="1">
+      <c r="A216" s="16" t="inlineStr">
+        <is>
+          <t>TERM-215</t>
+        </is>
+      </c>
+      <c r="B216" s="16" t="inlineStr">
+        <is>
+          <t>데이터·시맨틱·품질</t>
+        </is>
+      </c>
+      <c r="C216" s="16" t="inlineStr">
+        <is>
+          <t>Data, Semantics &amp; Quality</t>
+        </is>
+      </c>
+      <c r="D216" s="16" t="inlineStr">
+        <is>
+          <t>평가 지표</t>
+        </is>
+      </c>
+      <c r="E216" s="16" t="inlineStr">
+        <is>
+          <t>Evaluation Metrics</t>
+        </is>
+      </c>
+      <c r="F216" s="16" t="inlineStr">
+        <is>
+          <t>평가 지표</t>
+        </is>
+      </c>
+      <c r="G216" s="16" t="inlineStr">
+        <is>
+          <t>Two-stage validation (historical → real-time)</t>
+        </is>
+      </c>
+      <c r="H216" s="16" t="inlineStr">
+        <is>
+          <t>2단계 검증(과거→실시간)</t>
+        </is>
+      </c>
+      <c r="I216" s="16" t="inlineStr">
+        <is>
+          <t>TWO_STAGE_VALIDATION</t>
+        </is>
+      </c>
+      <c r="J216" s="16" t="inlineStr">
+        <is>
+          <t>1차 과거 데이터 검증; 2차 실시간 적용 검증; two-step validation</t>
+        </is>
+      </c>
+      <c r="K216" s="16" t="inlineStr">
+        <is>
+          <t>QualityProcess</t>
+        </is>
+      </c>
+      <c r="L216" s="16" t="inlineStr">
+        <is>
+          <t>G1·G2 산출물의 신뢰도 평가 체계 — ①약 15개년 과거 데이터로 규칙·순위를 검증(H1~H5) ②실시간 수집 데이터 유형별로 같은 규칙이 성립하는지 재검증(R1~R6). 승인자 요구(2026-09-14)</t>
+        </is>
+      </c>
+      <c r="M216" s="16" t="inlineStr">
+        <is>
+          <t>두 단계 수치는 예측 정확도가 아니라 과정 무결성·과거 관측 요약임(A-191) · 브리프 신뢰도 블록과 월별 부록에 같은 정의로 표시</t>
+        </is>
+      </c>
+      <c r="N216" s="16" t="inlineStr">
+        <is>
+          <t>Governance</t>
+        </is>
+      </c>
+      <c r="O216" s="16" t="inlineStr">
+        <is>
+          <t>CONTEXT</t>
+        </is>
+      </c>
+      <c r="P216" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q216" s="16" t="inlineStr">
+        <is>
+          <t>g1_reliability_latest.json 미산출 시 브리프에 미산출 표기</t>
+        </is>
+      </c>
+      <c r="R216" s="16" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="S216" s="16" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="T216" s="16" t="inlineStr">
+        <is>
+          <t>Evaluation</t>
+        </is>
+      </c>
+      <c r="U216" s="16" t="inlineStr">
+        <is>
+          <t>MEASURES</t>
+        </is>
+      </c>
+      <c r="V216" s="16" t="inlineStr">
+        <is>
+          <t>src/evaluation/g1_reliability.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="217" ht="42" customHeight="1">
+      <c r="A217" s="16" t="inlineStr">
+        <is>
+          <t>TERM-216</t>
+        </is>
+      </c>
+      <c r="B217" s="16" t="inlineStr">
+        <is>
+          <t>데이터·시맨틱·품질</t>
+        </is>
+      </c>
+      <c r="C217" s="16" t="inlineStr">
+        <is>
+          <t>Data, Semantics &amp; Quality</t>
+        </is>
+      </c>
+      <c r="D217" s="16" t="inlineStr">
+        <is>
+          <t>평가 지표</t>
+        </is>
+      </c>
+      <c r="E217" s="16" t="inlineStr">
+        <is>
+          <t>Evaluation Metrics</t>
+        </is>
+      </c>
+      <c r="F217" s="16" t="inlineStr">
+        <is>
+          <t>평가 지표</t>
+        </is>
+      </c>
+      <c r="G217" s="16" t="inlineStr">
+        <is>
+          <t>Variable rank stability</t>
+        </is>
+      </c>
+      <c r="H217" s="16" t="inlineStr">
+        <is>
+          <t>변인 순위 안정성</t>
+        </is>
+      </c>
+      <c r="I217" s="16" t="inlineStr">
+        <is>
+          <t>RANK_STABILITY</t>
+        </is>
+      </c>
+      <c r="J217" s="16" t="inlineStr">
+        <is>
+          <t>Spearman rank stability; 순위 상관 안정성</t>
+        </is>
+      </c>
+      <c r="K217" s="16" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="L217" s="16" t="inlineStr">
+        <is>
+          <t>확장 폴드(5구간 누적)마다 |피어슨 r|(및 규제 회귀 계수) 순위를 만들어 인접 폴드 간 Spearman ρ와 상위 20 부호 일치율을 잰 값. 표본 추가에 순위가 흔들리지 않을수록 현재 핵심 변인 주장이 견고함</t>
+        </is>
+      </c>
+      <c r="M217" s="16" t="inlineStr">
+        <is>
+          <t>ρ는 -1~1 · 부호 일치율은 0~1 · 폴드 수와 상위 N 명시 필수 · 정본 입력(CI 마트)과 진단 입력(로컬) 라벨 구분</t>
+        </is>
+      </c>
+      <c r="N217" s="16" t="inlineStr">
+        <is>
+          <t>Governance</t>
+        </is>
+      </c>
+      <c r="O217" s="16" t="inlineStr">
+        <is>
+          <t>CONTEXT</t>
+        </is>
+      </c>
+      <c r="P217" s="16" t="inlineStr">
+        <is>
+          <t>ρ(-1~1)·비율(0~1)</t>
+        </is>
+      </c>
+      <c r="Q217" s="16" t="inlineStr">
+        <is>
+          <t>월별판 산출 · 임계 없음(추세 관찰)</t>
+        </is>
+      </c>
+      <c r="R217" s="16" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="S217" s="16" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="T217" s="16" t="inlineStr">
+        <is>
+          <t>QualityMetric</t>
+        </is>
+      </c>
+      <c r="U217" s="16" t="inlineStr">
+        <is>
+          <t>MEASURES</t>
+        </is>
+      </c>
+      <c r="V217" s="16" t="inlineStr">
+        <is>
+          <t>src/evaluation/g1_reliability.py::rank_stability</t>
+        </is>
+      </c>
+    </row>
+    <row r="218" ht="42" customHeight="1">
+      <c r="A218" s="16" t="inlineStr">
+        <is>
+          <t>TERM-217</t>
+        </is>
+      </c>
+      <c r="B218" s="16" t="inlineStr">
+        <is>
+          <t>데이터·시맨틱·품질</t>
+        </is>
+      </c>
+      <c r="C218" s="16" t="inlineStr">
+        <is>
+          <t>Data, Semantics &amp; Quality</t>
+        </is>
+      </c>
+      <c r="D218" s="16" t="inlineStr">
+        <is>
+          <t>평가 지표</t>
+        </is>
+      </c>
+      <c r="E218" s="16" t="inlineStr">
+        <is>
+          <t>Evaluation Metrics</t>
+        </is>
+      </c>
+      <c r="F218" s="16" t="inlineStr">
+        <is>
+          <t>평가 지표</t>
+        </is>
+      </c>
+      <c r="G218" s="16" t="inlineStr">
+        <is>
+          <t>Alert-rule retrospective score (false-alarm proxy)</t>
+        </is>
+      </c>
+      <c r="H218" s="16" t="inlineStr">
+        <is>
+          <t>경보 규칙 소급 성적(오경보 근사율)</t>
+        </is>
+      </c>
+      <c r="I218" s="16" t="inlineStr">
+        <is>
+          <t>ALERT_RETRO_FALSE_ALARM</t>
+        </is>
+      </c>
+      <c r="J218" s="16" t="inlineStr">
+        <is>
+          <t>false alarm proxy; 소급 합성 경보 성적</t>
+        </is>
+      </c>
+      <c r="K218" s="16" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="L218" s="16" t="inlineStr">
+        <is>
+          <t>현행 임계 규칙을 2010~2025에 소급 적용해 에피소드(간격≥지평)를 만들고, 경보 뒤 5/20/60거래일 |수익률|이 무조건부 중앙값 이하인 비율. 값이 50%면 규칙이 평소와 구분되지 않음</t>
+        </is>
+      </c>
+      <c r="M218" s="16" t="inlineStr">
+        <is>
+          <t>라벨 '실발행 아님 — 소급 합성' 고정 · 방향 적중률 산출 금지 · 에피소드 8회 미만 보류 · 규칙 버전 병기</t>
+        </is>
+      </c>
+      <c r="N218" s="16" t="inlineStr">
+        <is>
+          <t>Governance</t>
+        </is>
+      </c>
+      <c r="O218" s="16" t="inlineStr">
+        <is>
+          <t>CONTEXT</t>
+        </is>
+      </c>
+      <c r="P218" s="16" t="inlineStr">
+        <is>
+          <t>비율(0~1)·에피소드 수</t>
+        </is>
+      </c>
+      <c r="Q218" s="16" t="inlineStr">
+        <is>
+          <t>보류 기준 8회</t>
+        </is>
+      </c>
+      <c r="R218" s="16" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="S218" s="16" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="T218" s="16" t="inlineStr">
+        <is>
+          <t>QualityMetric</t>
+        </is>
+      </c>
+      <c r="U218" s="16" t="inlineStr">
+        <is>
+          <t>MEASURES</t>
+        </is>
+      </c>
+      <c r="V218" s="16" t="inlineStr">
+        <is>
+          <t>src/evaluation/g1_reliability.py::alert_rule_retro</t>
+        </is>
+      </c>
+    </row>
+    <row r="219" ht="42" customHeight="1">
+      <c r="A219" s="16" t="inlineStr">
+        <is>
+          <t>TERM-218</t>
+        </is>
+      </c>
+      <c r="B219" s="16" t="inlineStr">
+        <is>
+          <t>데이터·시맨틱·품질</t>
+        </is>
+      </c>
+      <c r="C219" s="16" t="inlineStr">
+        <is>
+          <t>Data, Semantics &amp; Quality</t>
+        </is>
+      </c>
+      <c r="D219" s="16" t="inlineStr">
+        <is>
+          <t>평가 지표</t>
+        </is>
+      </c>
+      <c r="E219" s="16" t="inlineStr">
+        <is>
+          <t>Evaluation Metrics</t>
+        </is>
+      </c>
+      <c r="F219" s="16" t="inlineStr">
+        <is>
+          <t>평가 지표</t>
+        </is>
+      </c>
+      <c r="G219" s="16" t="inlineStr">
+        <is>
+          <t>Reference-range width diagnosis</t>
+        </is>
+      </c>
+      <c r="H219" s="16" t="inlineStr">
+        <is>
+          <t>참고 범위 폭 진단</t>
+        </is>
+      </c>
+      <c r="I219" s="16" t="inlineStr">
+        <is>
+          <t>RANGE_WIDTH_DIAG</t>
+        </is>
+      </c>
+      <c r="J219" s="16" t="inlineStr">
+        <is>
+          <t>empirical coverage of reference range; 참고 범위 포함률</t>
+        </is>
+      </c>
+      <c r="K219" s="16" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="L219" s="16" t="inlineStr">
+        <is>
+          <t>브리프 참고 범위(직전 h거래일 수익률의 P10~P90 확장 분위)가 실측 변동을 담은 비율과 평균 폭. 명목 80% 대비 부족분이 곧 범위 폭의 한계</t>
+        </is>
+      </c>
+      <c r="M219" s="16" t="inlineStr">
+        <is>
+          <t>확률 밴드 주장이 아니므로 의사결정 근거 금지(신뢰 문서 §2 ④) · 월별 부록 한정 · 스트레스 슬라이스별 병기</t>
+        </is>
+      </c>
+      <c r="N219" s="16" t="inlineStr">
+        <is>
+          <t>Governance</t>
+        </is>
+      </c>
+      <c r="O219" s="16" t="inlineStr">
+        <is>
+          <t>CONTEXT</t>
+        </is>
+      </c>
+      <c r="P219" s="16" t="inlineStr">
+        <is>
+          <t>비율(0~1)·폭(%)</t>
+        </is>
+      </c>
+      <c r="Q219" s="16" t="inlineStr">
+        <is>
+          <t>명목 80% 대비 편차 관찰</t>
+        </is>
+      </c>
+      <c r="R219" s="16" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="S219" s="16" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="T219" s="16" t="inlineStr">
+        <is>
+          <t>QualityMetric</t>
+        </is>
+      </c>
+      <c r="U219" s="16" t="inlineStr">
+        <is>
+          <t>MEASURES</t>
+        </is>
+      </c>
+      <c r="V219" s="16" t="inlineStr">
+        <is>
+          <t>src/evaluation/g1_reliability.py::reference_range_diagnosis</t>
+        </is>
+      </c>
+    </row>
+    <row r="220" ht="42" customHeight="1">
+      <c r="A220" s="16" t="inlineStr">
+        <is>
+          <t>TERM-219</t>
+        </is>
+      </c>
+      <c r="B220" s="16" t="inlineStr">
+        <is>
+          <t>데이터·시맨틱·품질</t>
+        </is>
+      </c>
+      <c r="C220" s="16" t="inlineStr">
+        <is>
+          <t>Data, Semantics &amp; Quality</t>
+        </is>
+      </c>
+      <c r="D220" s="16" t="inlineStr">
+        <is>
+          <t>평가 지표</t>
+        </is>
+      </c>
+      <c r="E220" s="16" t="inlineStr">
+        <is>
+          <t>Evaluation Metrics</t>
+        </is>
+      </c>
+      <c r="F220" s="16" t="inlineStr">
+        <is>
+          <t>평가 지표</t>
+        </is>
+      </c>
+      <c r="G220" s="16" t="inlineStr">
+        <is>
+          <t>Alert ledger</t>
+        </is>
+      </c>
+      <c r="H220" s="16" t="inlineStr">
+        <is>
+          <t>경보 원장</t>
+        </is>
+      </c>
+      <c r="I220" s="16" t="inlineStr">
+        <is>
+          <t>ALERT_LEDGER</t>
+        </is>
+      </c>
+      <c r="J220" s="16" t="inlineStr">
+        <is>
+          <t>실발행 경보 원장; g1_alert_ledger</t>
+        </is>
+      </c>
+      <c r="K220" s="16" t="inlineStr">
+        <is>
+          <t>Metadata</t>
+        </is>
+      </c>
+      <c r="L220" s="16" t="inlineStr">
+        <is>
+          <t>G1이 실제 발행한 경보(변수·값·임계·규칙 버전·실행 ID)를 날짜별로 영구 기록하고, 5/20/60거래일 경과 후 실측 |수익률|을 채우는 표. 2026-09-14 개설(9/9·9/13 경보 시드)</t>
+        </is>
+      </c>
+      <c r="M220" s="16" t="inlineStr">
+        <is>
+          <t>(date, variable) 중복은 기존 유지 · 성숙 경보 8회 이상부터 사후 성적 표기 · look-ahead 차단(경과분만 채움)</t>
+        </is>
+      </c>
+      <c r="N220" s="16" t="inlineStr">
+        <is>
+          <t>Governance</t>
+        </is>
+      </c>
+      <c r="O220" s="16" t="inlineStr">
+        <is>
+          <t>CONTEXT</t>
+        </is>
+      </c>
+      <c r="P220" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q220" s="16" t="inlineStr">
+        <is>
+          <t>성숙 8회 미만 보류</t>
+        </is>
+      </c>
+      <c r="R220" s="16" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="S220" s="16" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="T220" s="16" t="inlineStr">
+        <is>
+          <t>ProvenanceRecord</t>
+        </is>
+      </c>
+      <c r="U220" s="16" t="inlineStr">
+        <is>
+          <t>PROVIDES</t>
+        </is>
+      </c>
+      <c r="V220" s="16" t="inlineStr">
+        <is>
+          <t>data/processed/g1_alert_ledger.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="221" ht="42" customHeight="1">
+      <c r="A221" s="16" t="inlineStr">
+        <is>
+          <t>TERM-220</t>
+        </is>
+      </c>
+      <c r="B221" s="16" t="inlineStr">
+        <is>
+          <t>데이터·시맨틱·품질</t>
+        </is>
+      </c>
+      <c r="C221" s="16" t="inlineStr">
+        <is>
+          <t>Data, Semantics &amp; Quality</t>
+        </is>
+      </c>
+      <c r="D221" s="16" t="inlineStr">
+        <is>
+          <t>평가 지표</t>
+        </is>
+      </c>
+      <c r="E221" s="16" t="inlineStr">
+        <is>
+          <t>Evaluation Metrics</t>
+        </is>
+      </c>
+      <c r="F221" s="16" t="inlineStr">
+        <is>
+          <t>평가 지표</t>
+        </is>
+      </c>
+      <c r="G221" s="16" t="inlineStr">
+        <is>
+          <t>Pinball loss</t>
+        </is>
+      </c>
+      <c r="H221" s="16" t="inlineStr">
+        <is>
+          <t>핀볼 손실</t>
+        </is>
+      </c>
+      <c r="I221" s="16" t="inlineStr">
+        <is>
+          <t>PINBALL</t>
+        </is>
+      </c>
+      <c r="J221" s="16" t="inlineStr">
+        <is>
+          <t>quantile loss; 분위 손실</t>
+        </is>
+      </c>
+      <c r="K221" s="16" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="L221" s="16" t="inlineStr">
+        <is>
+          <t>분위 q 예측 qhat에 대한 손실 max(q(y−qhat), (q−1)(y−qhat))의 평균 — 분위 밴드의 정확도 척도. 낮을수록 좋음. 기준선 대비 상대 비교로만 해석</t>
+        </is>
+      </c>
+      <c r="M221" s="16" t="inlineStr">
+        <is>
+          <t>단일 점수 금지 — 지평×기준선×슬라이스 표로 보고(방법론 §Validation) · 로그수익률 단위 명시</t>
+        </is>
+      </c>
+      <c r="N221" s="16" t="inlineStr">
+        <is>
+          <t>Governance</t>
+        </is>
+      </c>
+      <c r="O221" s="16" t="inlineStr">
+        <is>
+          <t>CONTEXT</t>
+        </is>
+      </c>
+      <c r="P221" s="16" t="inlineStr">
+        <is>
+          <t>손실(≥0)</t>
+        </is>
+      </c>
+      <c r="Q221" s="16" t="inlineStr">
+        <is>
+          <t>기준선(최근값·롤링 분위) 미개선 시 승격 없음</t>
+        </is>
+      </c>
+      <c r="R221" s="16" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="S221" s="16" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="T221" s="16" t="inlineStr">
+        <is>
+          <t>QualityMetric</t>
+        </is>
+      </c>
+      <c r="U221" s="16" t="inlineStr">
+        <is>
+          <t>MEASURES</t>
+        </is>
+      </c>
+      <c r="V221" s="16" t="inlineStr">
+        <is>
+          <t>src/evaluation/band_backtest.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="222" ht="42" customHeight="1">
+      <c r="A222" s="16" t="inlineStr">
+        <is>
+          <t>TERM-221</t>
+        </is>
+      </c>
+      <c r="B222" s="16" t="inlineStr">
+        <is>
+          <t>데이터·시맨틱·품질</t>
+        </is>
+      </c>
+      <c r="C222" s="16" t="inlineStr">
+        <is>
+          <t>Data, Semantics &amp; Quality</t>
+        </is>
+      </c>
+      <c r="D222" s="16" t="inlineStr">
+        <is>
+          <t>평가 지표</t>
+        </is>
+      </c>
+      <c r="E222" s="16" t="inlineStr">
+        <is>
+          <t>Evaluation Metrics</t>
+        </is>
+      </c>
+      <c r="F222" s="16" t="inlineStr">
+        <is>
+          <t>평가 지표</t>
+        </is>
+      </c>
+      <c r="G222" s="16" t="inlineStr">
+        <is>
+          <t>Empirical interval coverage</t>
+        </is>
+      </c>
+      <c r="H222" s="16" t="inlineStr">
+        <is>
+          <t>경험 구간 포함률</t>
+        </is>
+      </c>
+      <c r="I222" s="16" t="inlineStr">
+        <is>
+          <t>COVERAGE</t>
+        </is>
+      </c>
+      <c r="J222" s="16" t="inlineStr">
+        <is>
+          <t>empirical coverage; 밴드 포함률</t>
+        </is>
+      </c>
+      <c r="K222" s="16" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="L222" s="16" t="inlineStr">
+        <is>
+          <t>명목 50%/80% 구간에 실측이 든 비율. 명목과의 차이가 밴드 보정(EnCQR) 필요성의 지표</t>
+        </is>
+      </c>
+      <c r="M222" s="16" t="inlineStr">
+        <is>
+          <t>레짐·스트레스 슬라이스별 분리 보고 필수 · 명목 초과도 결함(폭 과대)</t>
+        </is>
+      </c>
+      <c r="N222" s="16" t="inlineStr">
+        <is>
+          <t>Governance</t>
+        </is>
+      </c>
+      <c r="O222" s="16" t="inlineStr">
+        <is>
+          <t>CONTEXT</t>
+        </is>
+      </c>
+      <c r="P222" s="16" t="inlineStr">
+        <is>
+          <t>비율(0~1)</t>
+        </is>
+      </c>
+      <c r="Q222" s="16" t="inlineStr">
+        <is>
+          <t>명목 ±5%p 밖이면 보정 대상(INFERENCE)</t>
+        </is>
+      </c>
+      <c r="R222" s="16" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="S222" s="16" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="T222" s="16" t="inlineStr">
+        <is>
+          <t>QualityMetric</t>
+        </is>
+      </c>
+      <c r="U222" s="16" t="inlineStr">
+        <is>
+          <t>MEASURES</t>
+        </is>
+      </c>
+      <c r="V222" s="16" t="inlineStr">
+        <is>
+          <t>src/evaluation/band_backtest.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="223" ht="42" customHeight="1">
+      <c r="A223" s="16" t="inlineStr">
+        <is>
+          <t>TERM-222</t>
+        </is>
+      </c>
+      <c r="B223" s="16" t="inlineStr">
+        <is>
+          <t>데이터·시맨틱·품질</t>
+        </is>
+      </c>
+      <c r="C223" s="16" t="inlineStr">
+        <is>
+          <t>Data, Semantics &amp; Quality</t>
+        </is>
+      </c>
+      <c r="D223" s="16" t="inlineStr">
+        <is>
+          <t>평가 지표</t>
+        </is>
+      </c>
+      <c r="E223" s="16" t="inlineStr">
+        <is>
+          <t>Evaluation Metrics</t>
+        </is>
+      </c>
+      <c r="F223" s="16" t="inlineStr">
+        <is>
+          <t>평가 지표</t>
+        </is>
+      </c>
+      <c r="G223" s="16" t="inlineStr">
+        <is>
+          <t>Walk-forward validation</t>
+        </is>
+      </c>
+      <c r="H223" s="16" t="inlineStr">
+        <is>
+          <t>워크포워드 검증</t>
+        </is>
+      </c>
+      <c r="I223" s="16" t="inlineStr">
+        <is>
+          <t>WALK_FORWARD</t>
+        </is>
+      </c>
+      <c r="J223" s="16" t="inlineStr">
+        <is>
+          <t>expanding window CV; 시간순 교차검증</t>
+        </is>
+      </c>
+      <c r="K223" s="16" t="inlineStr">
+        <is>
+          <t>GovernanceProcess</t>
+        </is>
+      </c>
+      <c r="L223" s="16" t="inlineStr">
+        <is>
+          <t>시간 순서를 지키는 확장/이동 창 검증 — 각 시점의 예측은 그 시점까지 확정된 정보만 사용. 무작위 분할은 금지(M-001)</t>
+        </is>
+      </c>
+      <c r="M223" s="16" t="inlineStr">
+        <is>
+          <t>전처리·분위 추정을 폴드 안에서 재적합 · gap=지평으로 전방 창 겹침 차단</t>
+        </is>
+      </c>
+      <c r="N223" s="16" t="inlineStr">
+        <is>
+          <t>Governance</t>
+        </is>
+      </c>
+      <c r="O223" s="16" t="inlineStr">
+        <is>
+          <t>CONTEXT</t>
+        </is>
+      </c>
+      <c r="P223" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q223" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R223" s="16" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="S223" s="16" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="T223" s="16" t="inlineStr">
+        <is>
+          <t>ReviewProcess</t>
+        </is>
+      </c>
+      <c r="U223" s="16" t="inlineStr">
+        <is>
+          <t>APPLIES_TO</t>
+        </is>
+      </c>
+      <c r="V223" s="16" t="inlineStr">
+        <is>
+          <t>src/evaluation/band_backtest.py,.claude/rules/modeling.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="224" ht="42" customHeight="1">
+      <c r="A224" s="16" t="inlineStr">
+        <is>
+          <t>TERM-223</t>
+        </is>
+      </c>
+      <c r="B224" s="16" t="inlineStr">
+        <is>
+          <t>데이터·시맨틱·품질</t>
+        </is>
+      </c>
+      <c r="C224" s="16" t="inlineStr">
+        <is>
+          <t>Data, Semantics &amp; Quality</t>
+        </is>
+      </c>
+      <c r="D224" s="16" t="inlineStr">
+        <is>
+          <t>평가 지표</t>
+        </is>
+      </c>
+      <c r="E224" s="16" t="inlineStr">
+        <is>
+          <t>Evaluation Metrics</t>
+        </is>
+      </c>
+      <c r="F224" s="16" t="inlineStr">
+        <is>
+          <t>평가 지표</t>
+        </is>
+      </c>
+      <c r="G224" s="16" t="inlineStr">
+        <is>
+          <t>Lockbox period</t>
+        </is>
+      </c>
+      <c r="H224" s="16" t="inlineStr">
+        <is>
+          <t>락박스 기간</t>
+        </is>
+      </c>
+      <c r="I224" s="16" t="inlineStr">
+        <is>
+          <t>LOCKBOX</t>
+        </is>
+      </c>
+      <c r="J224" s="16" t="inlineStr">
+        <is>
+          <t>hold-out latest period; 최신 보존 기간</t>
+        </is>
+      </c>
+      <c r="K224" s="16" t="inlineStr">
+        <is>
+          <t>GovernanceProcess</t>
+        </is>
+      </c>
+      <c r="L224" s="16" t="inlineStr">
+        <is>
+          <t>최신 완전 기간(현행 2025-07~12)을 학습·튜닝에서 분리해 마지막에 한 번만 평가하는 규약</t>
+        </is>
+      </c>
+      <c r="M224" s="16" t="inlineStr">
+        <is>
+          <t>락박스 성적은 별도 열로 표기 · 튜닝 반복 후 재사용 금지</t>
+        </is>
+      </c>
+      <c r="N224" s="16" t="inlineStr">
+        <is>
+          <t>Governance</t>
+        </is>
+      </c>
+      <c r="O224" s="16" t="inlineStr">
+        <is>
+          <t>CONTEXT</t>
+        </is>
+      </c>
+      <c r="P224" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q224" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R224" s="16" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="S224" s="16" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="T224" s="16" t="inlineStr">
+        <is>
+          <t>ReviewProcess</t>
+        </is>
+      </c>
+      <c r="U224" s="16" t="inlineStr">
+        <is>
+          <t>APPLIES_TO</t>
+        </is>
+      </c>
+      <c r="V224" s="16" t="inlineStr">
+        <is>
+          <t>src/evaluation/band_backtest.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="225" ht="42" customHeight="1">
+      <c r="A225" s="16" t="inlineStr">
+        <is>
+          <t>TERM-224</t>
+        </is>
+      </c>
+      <c r="B225" s="16" t="inlineStr">
+        <is>
+          <t>데이터·시맨틱·품질</t>
+        </is>
+      </c>
+      <c r="C225" s="16" t="inlineStr">
+        <is>
+          <t>Data, Semantics &amp; Quality</t>
+        </is>
+      </c>
+      <c r="D225" s="16" t="inlineStr">
+        <is>
+          <t>평가 지표</t>
+        </is>
+      </c>
+      <c r="E225" s="16" t="inlineStr">
+        <is>
+          <t>Evaluation Metrics</t>
+        </is>
+      </c>
+      <c r="F225" s="16" t="inlineStr">
+        <is>
+          <t>평가 지표</t>
+        </is>
+      </c>
+      <c r="G225" s="16" t="inlineStr">
+        <is>
+          <t>Forecast issue date / valid date / lead</t>
+        </is>
+      </c>
+      <c r="H225" s="16" t="inlineStr">
+        <is>
+          <t>예보 발행일·유효일·리드</t>
+        </is>
+      </c>
+      <c r="I225" s="16" t="inlineStr">
+        <is>
+          <t>FCST_ISSUE_VALID_LEAD</t>
+        </is>
+      </c>
+      <c r="J225" s="16" t="inlineStr">
+        <is>
+          <t>issue_date; valid_date; lead_days</t>
+        </is>
+      </c>
+      <c r="K225" s="16" t="inlineStr">
+        <is>
+          <t>DateAttribute</t>
+        </is>
+      </c>
+      <c r="L225" s="16" t="inlineStr">
+        <is>
+          <t>산지 15일 예보 행의 시간 규약 — 발행일(수집일)이 as-of 키(price_date=event_time), 유효일은 별도 열, 리드=유효일−발행일(0~16). 2026-09-14(A-263)부터 별도 파케이 climate_forecast</t>
+        </is>
+      </c>
+      <c r="M225" s="16" t="inlineStr">
+        <is>
+          <t>예보와 관측을 같은 코드·파일에 섞지 않음 · 마트 미등재(skill 검증 전 모델 투입 금지) · 같은 유효일이 매일 재예보되므로 발행일이 vintage</t>
+        </is>
+      </c>
+      <c r="N225" s="16" t="inlineStr">
+        <is>
+          <t>Supply</t>
+        </is>
+      </c>
+      <c r="O225" s="16" t="inlineStr">
+        <is>
+          <t>CONTEXT</t>
+        </is>
+      </c>
+      <c r="P225" s="16" t="inlineStr">
+        <is>
+          <t>일(0~16)</t>
+        </is>
+      </c>
+      <c r="Q225" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R225" s="16" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="S225" s="16" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="T225" s="16" t="inlineStr">
+        <is>
+          <t>TemporalAttribute</t>
+        </is>
+      </c>
+      <c r="U225" s="16" t="inlineStr">
+        <is>
+          <t>APPLIES_TO</t>
+        </is>
+      </c>
+      <c r="V225" s="16" t="inlineStr">
+        <is>
+          <t>data/schemas/climate_forecast.yaml</t>
+        </is>
+      </c>
+    </row>
+    <row r="226" ht="42" customHeight="1">
+      <c r="A226" s="16" t="inlineStr">
+        <is>
+          <t>TERM-225</t>
+        </is>
+      </c>
+      <c r="B226" s="16" t="inlineStr">
+        <is>
+          <t>데이터·시맨틱·품질</t>
+        </is>
+      </c>
+      <c r="C226" s="16" t="inlineStr">
+        <is>
+          <t>Data, Semantics &amp; Quality</t>
+        </is>
+      </c>
+      <c r="D226" s="16" t="inlineStr">
+        <is>
+          <t>무료 대안 소스</t>
+        </is>
+      </c>
+      <c r="E226" s="16" t="inlineStr">
+        <is>
+          <t>Free Alternative Sources</t>
+        </is>
+      </c>
+      <c r="F226" s="16" t="inlineStr">
+        <is>
+          <t>무료 대안 소스</t>
+        </is>
+      </c>
+      <c r="G226" s="16" t="inlineStr">
+        <is>
+          <t>stooq (free market data CSV)</t>
+        </is>
+      </c>
+      <c r="H226" s="16" t="inlineStr">
+        <is>
+          <t>stooq 무료 시세 CSV</t>
+        </is>
+      </c>
+      <c r="I226" s="16" t="inlineStr">
+        <is>
+          <t>STOOQ</t>
+        </is>
+      </c>
+      <c r="J226" s="16" t="inlineStr">
+        <is>
+          <t>stooq.com; ^bdi</t>
+        </is>
+      </c>
+      <c r="K226" s="16" t="inlineStr">
+        <is>
+          <t>DataSource</t>
+        </is>
+      </c>
+      <c r="L226" s="16" t="inlineStr">
+        <is>
+          <t>폴란드 기반 무료 시세 포털 — 일별 OHLC CSV 직접 다운로드(키 불요). 프로젝트에서는 BDI 2순위 폴백(A-053). 2026-08 실측에서 ^bdi 404(심볼 소멸) — 상태 재확인 대상</t>
+        </is>
+      </c>
+      <c r="M226" s="16" t="inlineStr">
+        <is>
+          <t>무료·비공식 소스이므로 정본 아님 · 심볼 소멸·형식 변경 시 폴백 체인 다음 단계로 이동 · 상업 이용 약관 확인 필요(DATA GAP)</t>
+        </is>
+      </c>
+      <c r="N226" s="16" t="inlineStr">
+        <is>
+          <t>Supply</t>
+        </is>
+      </c>
+      <c r="O226" s="16" t="inlineStr">
+        <is>
+          <t>CONTEXT</t>
+        </is>
+      </c>
+      <c r="P226" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q226" s="16" t="inlineStr">
+        <is>
+          <t>404 지속 시 체인에서 제거 검토</t>
+        </is>
+      </c>
+      <c r="R226" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="S226" s="16" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="T226" s="16" t="inlineStr">
+        <is>
+          <t>DataSource</t>
+        </is>
+      </c>
+      <c r="U226" s="16" t="inlineStr">
+        <is>
+          <t>PROVIDES</t>
+        </is>
+      </c>
+      <c r="V226" s="16" t="inlineStr">
+        <is>
+          <t>src/pipeline/connectors/shipping_connector.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="227" ht="42" customHeight="1">
+      <c r="A227" s="16" t="inlineStr">
+        <is>
+          <t>TERM-226</t>
+        </is>
+      </c>
+      <c r="B227" s="16" t="inlineStr">
+        <is>
+          <t>데이터·시맨틱·품질</t>
+        </is>
+      </c>
+      <c r="C227" s="16" t="inlineStr">
+        <is>
+          <t>Data, Semantics &amp; Quality</t>
+        </is>
+      </c>
+      <c r="D227" s="16" t="inlineStr">
+        <is>
+          <t>무료 대안 소스</t>
+        </is>
+      </c>
+      <c r="E227" s="16" t="inlineStr">
+        <is>
+          <t>Free Alternative Sources</t>
+        </is>
+      </c>
+      <c r="F227" s="16" t="inlineStr">
+        <is>
+          <t>무료 대안 소스</t>
+        </is>
+      </c>
+      <c r="G227" s="16" t="inlineStr">
+        <is>
+          <t>CFTC Commitments of Traders</t>
+        </is>
+      </c>
+      <c r="H227" s="16" t="inlineStr">
+        <is>
+          <t>CFTC 투기 포지션 보고(COT)</t>
+        </is>
+      </c>
+      <c r="I227" s="16" t="inlineStr">
+        <is>
+          <t>CFTC_COT</t>
+        </is>
+      </c>
+      <c r="J227" s="16" t="inlineStr">
+        <is>
+          <t>Commitments of Traders; publicreporting.cftc.gov</t>
+        </is>
+      </c>
+      <c r="K227" s="16" t="inlineStr">
+        <is>
+          <t>DataSource</t>
+        </is>
+      </c>
+      <c r="L227" s="16" t="inlineStr">
+        <is>
+          <t>미국 상품선물거래위원회 주간 포지션 보고 — 화요일 기준·금요일 15:30 ET 공표, 대두유(ZL) 상업/비상업 순포지션. 무료·공개 API/CSV. 미구현 무료 자산(P0, B-9)</t>
+        </is>
+      </c>
+      <c r="M227" s="16" t="inlineStr">
+        <is>
+          <t>발표 규칙 lag 3일(화→금) · 주간 지표는 as-of 발표일 이후 가용 · CE-017 근거 지표 후보</t>
+        </is>
+      </c>
+      <c r="N227" s="16" t="inlineStr">
+        <is>
+          <t>Demand</t>
+        </is>
+      </c>
+      <c r="O227" s="16" t="inlineStr">
+        <is>
+          <t>CONTEXT</t>
+        </is>
+      </c>
+      <c r="P227" s="16" t="inlineStr">
+        <is>
+          <t>계약 수</t>
+        </is>
+      </c>
+      <c r="Q227" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R227" s="16" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="S227" s="16" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="T227" s="16" t="inlineStr">
+        <is>
+          <t>DataSource</t>
+        </is>
+      </c>
+      <c r="U227" s="16" t="inlineStr">
+        <is>
+          <t>PROVIDES</t>
+        </is>
+      </c>
+      <c r="V227" s="16" t="inlineStr">
+        <is>
+          <t>docs/research_desk/2026-09/free_alternatives_inventory_2026_09_14.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="228" ht="42" customHeight="1">
+      <c r="A228" s="16" t="inlineStr">
+        <is>
+          <t>TERM-227</t>
+        </is>
+      </c>
+      <c r="B228" s="16" t="inlineStr">
+        <is>
+          <t>데이터·시맨틱·품질</t>
+        </is>
+      </c>
+      <c r="C228" s="16" t="inlineStr">
+        <is>
+          <t>Data, Semantics &amp; Quality</t>
+        </is>
+      </c>
+      <c r="D228" s="16" t="inlineStr">
+        <is>
+          <t>무료 대안 소스</t>
+        </is>
+      </c>
+      <c r="E228" s="16" t="inlineStr">
+        <is>
+          <t>Free Alternative Sources</t>
+        </is>
+      </c>
+      <c r="F228" s="16" t="inlineStr">
+        <is>
+          <t>무료 대안 소스</t>
+        </is>
+      </c>
+      <c r="G228" s="16" t="inlineStr">
+        <is>
+          <t>MPOB monthly palm oil statistics</t>
+        </is>
+      </c>
+      <c r="H228" s="16" t="inlineStr">
+        <is>
+          <t>MPOB 월간 팜유 통계</t>
+        </is>
+      </c>
+      <c r="I228" s="16" t="inlineStr">
+        <is>
+          <t>MPOB_BEPI</t>
+        </is>
+      </c>
+      <c r="J228" s="16" t="inlineStr">
+        <is>
+          <t>bepi.mpob.gov.my; Malaysian Palm Oil Board</t>
+        </is>
+      </c>
+      <c r="K228" s="16" t="inlineStr">
+        <is>
+          <t>DataSource</t>
+        </is>
+      </c>
+      <c r="L228" s="16" t="inlineStr">
+        <is>
+          <t>말레이시아 팜유청 월간 생산·재고·수출 통계(무료 공개, 익월 10일경 발표). 유료 FCPO 일별 선물의 부분 대안(수급 축) — 가격 축은 대체 불가</t>
+        </is>
+      </c>
+      <c r="M228" s="16" t="inlineStr">
+        <is>
+          <t>월간·발표 지연 약 10일 · CE-015 대두유−팜유 가격 차이 레짐 판별 보조 · egress 기등재</t>
+        </is>
+      </c>
+      <c r="N228" s="16" t="inlineStr">
+        <is>
+          <t>Supply</t>
+        </is>
+      </c>
+      <c r="O228" s="16" t="inlineStr">
+        <is>
+          <t>CONTEXT</t>
+        </is>
+      </c>
+      <c r="P228" s="16" t="inlineStr">
+        <is>
+          <t>천 톤</t>
+        </is>
+      </c>
+      <c r="Q228" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R228" s="16" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="S228" s="16" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="T228" s="16" t="inlineStr">
+        <is>
+          <t>DataSource</t>
+        </is>
+      </c>
+      <c r="U228" s="16" t="inlineStr">
+        <is>
+          <t>PROVIDES</t>
+        </is>
+      </c>
+      <c r="V228" s="16" t="inlineStr">
+        <is>
+          <t>docs/infra/egress_allowlist.yaml</t>
+        </is>
+      </c>
+    </row>
+    <row r="229" ht="42" customHeight="1">
+      <c r="A229" s="16" t="inlineStr">
+        <is>
+          <t>TERM-228</t>
+        </is>
+      </c>
+      <c r="B229" s="16" t="inlineStr">
+        <is>
+          <t>데이터·시맨틱·품질</t>
+        </is>
+      </c>
+      <c r="C229" s="16" t="inlineStr">
+        <is>
+          <t>Data, Semantics &amp; Quality</t>
+        </is>
+      </c>
+      <c r="D229" s="16" t="inlineStr">
+        <is>
+          <t>무료 대안 소스</t>
+        </is>
+      </c>
+      <c r="E229" s="16" t="inlineStr">
+        <is>
+          <t>Free Alternative Sources</t>
+        </is>
+      </c>
+      <c r="F229" s="16" t="inlineStr">
+        <is>
+          <t>무료 대안 소스</t>
+        </is>
+      </c>
+      <c r="G229" s="16" t="inlineStr">
+        <is>
+          <t>ECMWF Open Data (IFS/AIFS forecasts)</t>
+        </is>
+      </c>
+      <c r="H229" s="16" t="inlineStr">
+        <is>
+          <t>ECMWF 오픈 데이터(IFS·AIFS 예보)</t>
+        </is>
+      </c>
+      <c r="I229" s="16" t="inlineStr">
+        <is>
+          <t>ECMWF_OPEN_DATA</t>
+        </is>
+      </c>
+      <c r="J229" s="16" t="inlineStr">
+        <is>
+          <t>ecmwf-opendata; AIFS open forecast</t>
+        </is>
+      </c>
+      <c r="K229" s="16" t="inlineStr">
+        <is>
+          <t>DataSource</t>
+        </is>
+      </c>
+      <c r="L229" s="16" t="inlineStr">
+        <is>
+          <t>유럽중기예보센터가 공개하는 0.25° 실시간 예보(IFS·AIFS, CC BY 4.0). Open-Meteo 상용 조건(DQ-26)의 무료 대안 후보 — 점 추출·후처리 구현 필요</t>
+        </is>
+      </c>
+      <c r="M229" s="16" t="inlineStr">
+        <is>
+          <t>라이선스 표기 필수 · 원시 GRIB 처리 비용 · Open-Meteo best_match와 동일 계열이므로 skill 비교 가능</t>
+        </is>
+      </c>
+      <c r="N229" s="16" t="inlineStr">
+        <is>
+          <t>Supply</t>
+        </is>
+      </c>
+      <c r="O229" s="16" t="inlineStr">
+        <is>
+          <t>CONTEXT</t>
+        </is>
+      </c>
+      <c r="P229" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q229" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R229" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="S229" s="16" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="T229" s="16" t="inlineStr">
+        <is>
+          <t>DataSource</t>
+        </is>
+      </c>
+      <c r="U229" s="16" t="inlineStr">
+        <is>
+          <t>PROVIDES</t>
+        </is>
+      </c>
+      <c r="V229" s="16" t="inlineStr">
+        <is>
+          <t>docs/research_desk/2026-09/free_alternatives_inventory_2026_09_14.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="230" ht="42" customHeight="1">
+      <c r="A230" s="16" t="inlineStr">
+        <is>
+          <t>TERM-229</t>
+        </is>
+      </c>
+      <c r="B230" s="16" t="inlineStr">
+        <is>
+          <t>데이터·시맨틱·품질</t>
+        </is>
+      </c>
+      <c r="C230" s="16" t="inlineStr">
+        <is>
+          <t>Data, Semantics &amp; Quality</t>
+        </is>
+      </c>
+      <c r="D230" s="16" t="inlineStr">
+        <is>
+          <t>무료 대안 소스</t>
+        </is>
+      </c>
+      <c r="E230" s="16" t="inlineStr">
+        <is>
+          <t>Free Alternative Sources</t>
+        </is>
+      </c>
+      <c r="F230" s="16" t="inlineStr">
+        <is>
+          <t>무료 대안 소스</t>
+        </is>
+      </c>
+      <c r="G230" s="16" t="inlineStr">
+        <is>
+          <t>World Bank Pink Sheet (monthly commodity prices)</t>
+        </is>
+      </c>
+      <c r="H230" s="16" t="inlineStr">
+        <is>
+          <t>세계은행 월간 원자재 가격(핑크 시트)</t>
+        </is>
+      </c>
+      <c r="I230" s="16" t="inlineStr">
+        <is>
+          <t>WB_PINK_SHEET</t>
+        </is>
+      </c>
+      <c r="J230" s="16" t="inlineStr">
+        <is>
+          <t>Commodity Markets Outlook prices; CMO monthly</t>
+        </is>
+      </c>
+      <c r="K230" s="16" t="inlineStr">
+        <is>
+          <t>DataSource</t>
+        </is>
+      </c>
+      <c r="L230" s="16" t="inlineStr">
+        <is>
+          <t>세계은행 월간 원자재 가격표(대두유·팜유·해바라기유·유채유 등, USD/MT, 무료 xlsx). 유료 일별 유지류 시세의 월간 대안 — 일별 밀도는 대체 불가</t>
+        </is>
+      </c>
+      <c r="M230" s="16" t="inlineStr">
+        <is>
+          <t>월간·발표 지연 약 1주 · 스프레드 레짐의 장기 검증용 · 일별 마트 편입 시 as-of 발표일 규칙 필요</t>
+        </is>
+      </c>
+      <c r="N230" s="16" t="inlineStr">
+        <is>
+          <t>Supply</t>
+        </is>
+      </c>
+      <c r="O230" s="16" t="inlineStr">
+        <is>
+          <t>CONTEXT</t>
+        </is>
+      </c>
+      <c r="P230" s="16" t="inlineStr">
+        <is>
+          <t>USD/MT</t>
+        </is>
+      </c>
+      <c r="Q230" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R230" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="S230" s="16" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="T230" s="16" t="inlineStr">
+        <is>
+          <t>DataSource</t>
+        </is>
+      </c>
+      <c r="U230" s="16" t="inlineStr">
+        <is>
+          <t>PROVIDES</t>
+        </is>
+      </c>
+      <c r="V230" s="16" t="inlineStr">
+        <is>
+          <t>docs/research_desk/2026-09/free_alternatives_inventory_2026_09_14.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="231" ht="42" customHeight="1">
+      <c r="A231" s="16" t="inlineStr">
+        <is>
+          <t>TERM-230</t>
+        </is>
+      </c>
+      <c r="B231" s="16" t="inlineStr">
+        <is>
+          <t>데이터·시맨틱·품질</t>
+        </is>
+      </c>
+      <c r="C231" s="16" t="inlineStr">
+        <is>
+          <t>Data, Semantics &amp; Quality</t>
+        </is>
+      </c>
+      <c r="D231" s="16" t="inlineStr">
+        <is>
+          <t>무료 대안 소스</t>
+        </is>
+      </c>
+      <c r="E231" s="16" t="inlineStr">
+        <is>
+          <t>Free Alternative Sources</t>
+        </is>
+      </c>
+      <c r="F231" s="16" t="inlineStr">
+        <is>
+          <t>무료 대안 소스</t>
+        </is>
+      </c>
+      <c r="G231" s="16" t="inlineStr">
+        <is>
+          <t>USDA AMS weekly soybean oil cash prices</t>
+        </is>
+      </c>
+      <c r="H231" s="16" t="inlineStr">
+        <is>
+          <t>USDA AMS 주간 대두유 현물가</t>
+        </is>
+      </c>
+      <c r="I231" s="16" t="inlineStr">
+        <is>
+          <t>USDA_AMS_SBO</t>
+        </is>
+      </c>
+      <c r="J231" s="16" t="inlineStr">
+        <is>
+          <t>AMS Market News; National Weekly Soybean Oil</t>
+        </is>
+      </c>
+      <c r="K231" s="16" t="inlineStr">
+        <is>
+          <t>DataSource</t>
+        </is>
+      </c>
+      <c r="L231" s="16" t="inlineStr">
+        <is>
+          <t>미국 농무부 마케팅서비스 주간 현물(대두유·대두박) 보고 — 무료 공개. 유료 basis 호가(Platts/Fastmarkets)의 미국 내륙 현물 축 부분 대안(CFR 아시아 basis는 대체 불가)</t>
+        </is>
+      </c>
+      <c r="M231" s="16" t="inlineStr">
+        <is>
+          <t>주간·미국 내륙 기준 · CIF 아시아 호가와 NOT COMPARABLE · 기준 가격층 검증 보조</t>
+        </is>
+      </c>
+      <c r="N231" s="16" t="inlineStr">
+        <is>
+          <t>Supply</t>
+        </is>
+      </c>
+      <c r="O231" s="16" t="inlineStr">
+        <is>
+          <t>CONTEXT</t>
+        </is>
+      </c>
+      <c r="P231" s="16" t="inlineStr">
+        <is>
+          <t>USc/lb·USD/ton</t>
+        </is>
+      </c>
+      <c r="Q231" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R231" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="S231" s="16" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="T231" s="16" t="inlineStr">
+        <is>
+          <t>DataSource</t>
+        </is>
+      </c>
+      <c r="U231" s="16" t="inlineStr">
+        <is>
+          <t>PROVIDES</t>
+        </is>
+      </c>
+      <c r="V231" s="16" t="inlineStr">
+        <is>
+          <t>docs/research_desk/2026-09/free_alternatives_inventory_2026_09_14.md</t>
         </is>
       </c>
     </row>
@@ -24827,7 +26619,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F62"/>
+  <dimension ref="A1:F63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -26818,6 +28610,38 @@
       <c r="F62" s="17" t="inlineStr">
         <is>
           <t>Marketing Year price VALID_DURING Oct-Sep</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="39.95" customHeight="1">
+      <c r="A63" s="17" t="inlineStr">
+        <is>
+          <t>MEASURES</t>
+        </is>
+      </c>
+      <c r="B63" s="17" t="inlineStr">
+        <is>
+          <t>평가 지표·검증 절차가 산출물(경보·참고 범위·변인 순위·밴드)의 신뢰 속성을 측정함 (v3.4 — evaluation 층)</t>
+        </is>
+      </c>
+      <c r="C63" s="17" t="inlineStr">
+        <is>
+          <t>QualityMetric</t>
+        </is>
+      </c>
+      <c r="D63" s="17" t="inlineStr">
+        <is>
+          <t>Evaluation</t>
+        </is>
+      </c>
+      <c r="E63" s="17" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F63" s="17" t="inlineStr">
+        <is>
+          <t>참고 범위 폭 진단 MEASURES 일별 브리프 참고 범위</t>
         </is>
       </c>
     </row>
@@ -26835,7 +28659,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -27821,6 +29645,270 @@
       </c>
       <c r="E31" s="17" t="inlineStr"/>
       <c r="F31" s="17" t="inlineStr"/>
+    </row>
+    <row r="32" ht="44.1" customHeight="1">
+      <c r="A32" s="17" t="inlineStr">
+        <is>
+          <t>src/evaluation/g1_reliability.py</t>
+        </is>
+      </c>
+      <c r="B32" s="17" t="inlineStr">
+        <is>
+          <t>미등록</t>
+        </is>
+      </c>
+      <c r="C32" s="17" t="inlineStr">
+        <is>
+          <t>src/evaluation/g1_reliability.py</t>
+        </is>
+      </c>
+      <c r="D32" s="17" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E32" s="17" t="inlineStr"/>
+      <c r="F32" s="17" t="inlineStr"/>
+    </row>
+    <row r="33" ht="44.1" customHeight="1">
+      <c r="A33" s="17" t="inlineStr">
+        <is>
+          <t>src/evaluation/g1_reliability.py::rank_stability</t>
+        </is>
+      </c>
+      <c r="B33" s="17" t="inlineStr">
+        <is>
+          <t>미등록</t>
+        </is>
+      </c>
+      <c r="C33" s="17" t="inlineStr">
+        <is>
+          <t>src/evaluation/g1_reliability.py::rank_stability</t>
+        </is>
+      </c>
+      <c r="D33" s="17" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E33" s="17" t="inlineStr"/>
+      <c r="F33" s="17" t="inlineStr"/>
+    </row>
+    <row r="34" ht="44.1" customHeight="1">
+      <c r="A34" s="17" t="inlineStr">
+        <is>
+          <t>src/evaluation/g1_reliability.py::alert_rule_retro</t>
+        </is>
+      </c>
+      <c r="B34" s="17" t="inlineStr">
+        <is>
+          <t>미등록</t>
+        </is>
+      </c>
+      <c r="C34" s="17" t="inlineStr">
+        <is>
+          <t>src/evaluation/g1_reliability.py::alert_rule_retro</t>
+        </is>
+      </c>
+      <c r="D34" s="17" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E34" s="17" t="inlineStr"/>
+      <c r="F34" s="17" t="inlineStr"/>
+    </row>
+    <row r="35" ht="44.1" customHeight="1">
+      <c r="A35" s="17" t="inlineStr">
+        <is>
+          <t>src/evaluation/g1_reliability.py::reference_range_diagnosis</t>
+        </is>
+      </c>
+      <c r="B35" s="17" t="inlineStr">
+        <is>
+          <t>미등록</t>
+        </is>
+      </c>
+      <c r="C35" s="17" t="inlineStr">
+        <is>
+          <t>src/evaluation/g1_reliability.py::reference_range_diagnosis</t>
+        </is>
+      </c>
+      <c r="D35" s="17" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E35" s="17" t="inlineStr"/>
+      <c r="F35" s="17" t="inlineStr"/>
+    </row>
+    <row r="36" ht="44.1" customHeight="1">
+      <c r="A36" s="17" t="inlineStr">
+        <is>
+          <t>data/processed/g1_alert_ledger.csv</t>
+        </is>
+      </c>
+      <c r="B36" s="17" t="inlineStr">
+        <is>
+          <t>미등록</t>
+        </is>
+      </c>
+      <c r="C36" s="17" t="inlineStr">
+        <is>
+          <t>data/processed/g1_alert_ledger.csv</t>
+        </is>
+      </c>
+      <c r="D36" s="17" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E36" s="17" t="inlineStr"/>
+      <c r="F36" s="17" t="inlineStr"/>
+    </row>
+    <row r="37" ht="44.1" customHeight="1">
+      <c r="A37" s="17" t="inlineStr">
+        <is>
+          <t>src/evaluation/band_backtest.py</t>
+        </is>
+      </c>
+      <c r="B37" s="17" t="inlineStr">
+        <is>
+          <t>미등록</t>
+        </is>
+      </c>
+      <c r="C37" s="17" t="inlineStr">
+        <is>
+          <t>src/evaluation/band_backtest.py</t>
+        </is>
+      </c>
+      <c r="D37" s="17" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E37" s="17" t="inlineStr"/>
+      <c r="F37" s="17" t="inlineStr"/>
+    </row>
+    <row r="38" ht="44.1" customHeight="1">
+      <c r="A38" s="17" t="inlineStr">
+        <is>
+          <t>.claude/rules/modeling.md</t>
+        </is>
+      </c>
+      <c r="B38" s="17" t="inlineStr">
+        <is>
+          <t>미등록</t>
+        </is>
+      </c>
+      <c r="C38" s="17" t="inlineStr">
+        <is>
+          <t>.claude/rules/modeling.md</t>
+        </is>
+      </c>
+      <c r="D38" s="17" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E38" s="17" t="inlineStr"/>
+      <c r="F38" s="17" t="inlineStr"/>
+    </row>
+    <row r="39" ht="44.1" customHeight="1">
+      <c r="A39" s="17" t="inlineStr">
+        <is>
+          <t>data/schemas/climate_forecast.yaml</t>
+        </is>
+      </c>
+      <c r="B39" s="17" t="inlineStr">
+        <is>
+          <t>미등록</t>
+        </is>
+      </c>
+      <c r="C39" s="17" t="inlineStr">
+        <is>
+          <t>data/schemas/climate_forecast.yaml</t>
+        </is>
+      </c>
+      <c r="D39" s="17" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E39" s="17" t="inlineStr"/>
+      <c r="F39" s="17" t="inlineStr"/>
+    </row>
+    <row r="40" ht="44.1" customHeight="1">
+      <c r="A40" s="17" t="inlineStr">
+        <is>
+          <t>src/pipeline/connectors/shipping_connector.py</t>
+        </is>
+      </c>
+      <c r="B40" s="17" t="inlineStr">
+        <is>
+          <t>미등록</t>
+        </is>
+      </c>
+      <c r="C40" s="17" t="inlineStr">
+        <is>
+          <t>src/pipeline/connectors/shipping_connector.py</t>
+        </is>
+      </c>
+      <c r="D40" s="17" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E40" s="17" t="inlineStr"/>
+      <c r="F40" s="17" t="inlineStr"/>
+    </row>
+    <row r="41" ht="44.1" customHeight="1">
+      <c r="A41" s="17" t="inlineStr">
+        <is>
+          <t>docs/research_desk/2026-09/free_alternatives_inventory_2026_09_14.md</t>
+        </is>
+      </c>
+      <c r="B41" s="17" t="inlineStr">
+        <is>
+          <t>미등록</t>
+        </is>
+      </c>
+      <c r="C41" s="17" t="inlineStr">
+        <is>
+          <t>docs/research_desk/2026-09/free_alternatives_inventory_2026_09_14.md</t>
+        </is>
+      </c>
+      <c r="D41" s="17" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E41" s="17" t="inlineStr"/>
+      <c r="F41" s="17" t="inlineStr"/>
+    </row>
+    <row r="42" ht="44.1" customHeight="1">
+      <c r="A42" s="17" t="inlineStr">
+        <is>
+          <t>docs/infra/egress_allowlist.yaml</t>
+        </is>
+      </c>
+      <c r="B42" s="17" t="inlineStr">
+        <is>
+          <t>미등록</t>
+        </is>
+      </c>
+      <c r="C42" s="17" t="inlineStr">
+        <is>
+          <t>docs/infra/egress_allowlist.yaml</t>
+        </is>
+      </c>
+      <c r="D42" s="17" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E42" s="17" t="inlineStr"/>
+      <c r="F42" s="17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
